--- a/untitled folder/HSC_Physics_1st_Paper_Chapter_08_Periodic_Motion.xlsx
+++ b/untitled folder/HSC_Physics_1st_Paper_Chapter_08_Periodic_Motion.xlsx
@@ -1054,11 +1054,6 @@
           <t>একটি কণার সরল ছন্দিত স্পন্দনের ব্যবকলনীয় সমীকরণ $\frac{d^2 x}{dt^2} + \omega^2 x = 0$। এর সাধারণ সমাধান $x(t) = A\cos(\omega t + \phi)$ প্রতিপাদন কর এবং আদি শর্তাবলি ($t=0$-তে $x(0) = x_0$ এবং $v(0) = v_0$) দ্বারা বিস্তার $A$ ও আদি দশা $\phi$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>ধরা যাক $v = \frac{dx}{dt}$। তাহলে $\frac{d^2 x}{dt^2} = \frac{dv}{dt} = v\frac{dv}{dx}$। সমীকরণটি দাঁড়ায়: $v\frac{dv}{dx} + \omega^2 x = 0 \implies v dv = -\omega^2 x dx$। সমাকলন করি: $\frac{1}{2}v^2 = -\frac{1}{2}\omega^2 x^2 + C \implies v^2 = \omega^2(A^2 - x^2) \implies v = \frac{dx}{dt} = \omega\sqrt{A^2 - x^2}$। পুনরায় চলক পৃথক করে সমাকলন করি: $\int \frac{dx}{\sqrt{A^2 - x^2}} = \omega \int dt \implies \sin^{-1}\left(\frac{x}{A}\right) = \omega t + \phi' \implies x(t) = A\sin(\omega t + \phi') = A\cos(\omega t + \phi)$। আদি শর্তাবলি প্রয়োগ করি: $t=0$-তে $x(0) = A\cos\phi = x_0$ এবং বেগ $v(0) = -A\omega\sin\phi = v_0 \implies A\sin\phi = -\frac{v_0}{\omega}$। বর্গ করে যোগ করলে: $A^2(\cos^2\phi + \sin^2\phi) = x_0^2 + \frac{v_0^2}{\omega^2} \implies A = \sqrt{x_0^2 + \frac{v_0^2}{\omega^2}}$। ভাগ করে আদি দশা: $\tan\phi = -\frac{v_0}{\omega x_0}$।</t>
@@ -1104,11 +1099,6 @@
           <t>একটি কণা $A$ বিস্তার ও $T$ পর্যায়কাল নিয়ে সরল ছন্দিত গতিতে দুলছে। কণাটির (ক) সাম্যাবস্থা থেকে $x = A/2$-তে পৌঁছাতে এবং (খ) $x = A/2$ থেকে চরম প্রান্তে ($x = A$) পৌঁছাতে প্রয়োজনীয় সময়ের অনুপাত নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>সাম্যাবস্থা থেকে যাত্রা শুরু করলে সরণের সমীকরণ $x(t) = A\sin(\omega t)$। (ক) $x = A/2$ পৌঁছাতে সময় $t_1$: $A/2 = A\sin(\omega t_1) \implies \sin(\omega t_1) = \frac{1}{2} \implies \omega t_1 = \frac{\pi}{6} \implies \left(\frac{2\pi}{T}\right)t_1 = \frac{\pi}{6} \implies t_1 = \frac{T}{12}$। (খ) সাম্যাবস্থা থেকে চরম প্রান্ত $x = A$-তে পৌঁছাতে মোট সময় $t_{\text{total}} = \frac{T}{4}$। ফলে $x = A/2$ থেকে $x = A$-তে পৌঁছাতে সময় $t_2 = t_{\text{total}} - t_1 = \frac{T}{4} - \frac{T}{12} = \frac{3T - T}{12} = \frac{2T}{12} = \frac{T}{6}$। উভয় সময়ের অনুপাত: $\frac{t_1}{t_2} = \frac{T/12}{T/6} = \frac{1}{2} = 1:2$। অর্থাৎ সমান দূরত্ব হওয়া সত্ত্বেও শেষের অর্ধেকের গতিবেগ কমে যাওয়ায় দ্বিগুণ সময় লাগে।</t>
@@ -1154,11 +1144,6 @@
           <t>সরল ছন্দিত গতিসম্পন্ন একটি কণার সাম্যাবস্থা থেকে $x_1$ ও $x_2$ দূরত্বে বেগ যথাক্রমে $v_1$ ও $v_2$। কণাটির দোলনের পর্যায়কাল $T$ এবং বিস্তার $A$ এই রাশিগুলোর মাধ্যমে প্রকাশ কর।</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>বেগ ও সরণের সমীকরণ: $v^2 = \omega^2(A^2 - x^2)$। প্রদত্ত শর্তানুসারে: (১) $v_1^2 = \omega^2(A^2 - x_1^2) = \omega^2 A^2 - \omega^2 x_1^2$ এবং (২) $v_2^2 = \omega^2(A^2 - x_2^2) = \omega^2 A^2 - \omega^2 x_2^2$। সমীকরণ (১) থেকে (২) বিয়োগ করে পাই: $v_1^2 - v_2^2 = \omega^2(x_2^2 - x_1^2) \implies \omega^2 = \frac{v_1^2 - v_2^2}{x_2^2 - x_1^2} \implies \omega = \sqrt{\frac{v_1^2 - v_2^2}{x_2^2 - x_1^2}}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{x_2^2 - x_1^2}{v_1^2 - v_2^2}}$। সমীকরণ (১)-কে $x_2^2$ এবং (২)-কে $x_1^2$ দিয়ে গুণ করে বিয়োগ করলে পাওয়া যায় বিস্তার: $A = \sqrt{\frac{v_1^2 x_2^2 - v_2^2 x_1^2}{v_1^2 - v_2^2}}$।</t>
@@ -1255,11 +1240,6 @@
           <t>একটি কণার সরল ছন্দিত স্পন্দনে সর্বোচ্চ বেগ $v_{\max} = 10\text{ m/s}$ এবং সর্বোচ্চ ত্বরণ $a_{\max} = 40\text{ m/s}^2$। কণাটির কৌণিক কম্পাঙ্ক $\omega$, পর্যায়কাল $T$ এবং বিস্তার $A$ কত?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>আমরা জানি সাম্যাবস্থায় বেগ সর্বোচ্চ হয়: $v_{\max} = \omega A$। চরম প্রান্তে ত্বরণ সর্বোচ্চ হয়: $a_{\max} = \omega^2 A$। দুটি সমীকরণ ভাগ করে পাই: $\frac{a_{\max}}{v_{\max}} = \frac{\omega^2 A}{\omega A} = \omega \implies \omega = \frac{40}{10} = 4\text{ rad/s}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = \frac{2\pi}{4} = \frac{\pi}{2} \approx 1.571\text{ s}$। বিস্তার $A = \frac{v_{\max}}{\omega} = \frac{10}{4} = 2.5\text{ m}$।</t>
@@ -1305,11 +1285,6 @@
           <t>$A$ বিস্তার ও $T$ পর্যায়কালের সরল ছন্দিত গতিতে (ক) একটি পূর্ণ পর্যায়কালে গড় বেগ ও গড় দ্রুতি এবং (খ) এক প্রান্ত থেকে অন্য প্রান্তে গমনে গড় দ্রুতির মান কত?</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>(ক) একটি পূর্ণ পর্যায়কালে কণাটি আদি বিন্দুতে ফিরে আসে, ফলে মোট সরণ শূন্য। অতএব একটি পূর্ণ চক্রে গড় বেগ $\bar{v} = \frac{\Delta x}{T} = 0$। কিন্তু এক পূর্ণ চক্রে মোট অতিক্রান্ত পথদৈর্ঘ্য $4A$। ফলে এক পূর্ণ পর্যায়কালে গড় দ্রুতি $v_{\text{avg, full}} = \frac{4A}{T} = \frac{4A}{2\pi/\omega} = \frac{2}{\pi}\omega A = \frac{2}{\pi}v_{\max} \approx 0.637 v_{\max}$। (খ) এক প্রান্ত থেকে অন্য প্রান্তে যেতে সময় লাগে অর্ধ পর্যায়কাল $t = T/2$ এবং পথদৈর্ঘ্য $2A$। অতএব প্রান্তদ্বয়ের মধ্যবর্তী গড় দ্রুতি $v_{\text{avg, half}} = \frac{2A}{T/2} = \frac{4A}{T} = \frac{2}{\pi}v_{\max}$।</t>
@@ -1355,11 +1330,6 @@
           <t>সকল সরল ছন্দিত গতিই পর্যাবৃত্ত গতি কিন্তু সকল পর্যাবৃত্ত গতি সরল ছন্দিত গতি নয় কেন? গাণিতিক প্রত্যয়নী বলের শর্ত $F = -k x^n$ এর প্রেক্ষিতে ব্যাখ্যা কর।</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>পর্যাবৃত্ত গতির একমাত্র শর্ত হলো নির্দিষ্ট সময় পর পর কোনো গতি পুনরাবৃত্তি হওয়া ($f(t+T) = f(t)$), যেমন গ্রহের কক্ষপথীয় গতি বা দেয়াল ঘড়ির কাঁটার গতি। সরল ছন্দিত গতি (SHM) হলো পর্যাবৃত্ত গতির একটি বিশেষ রূপ যেখানে প্রত্যয়নী বল সর্বদা সাম্যাবস্থা অভিমুখী এবং সরণের প্রথম ঘাতের সমানুপাতিক: $F = -k x^1$ (অর্থাৎ $n=1$)। যদি প্রত্যয়নী বলের ঘাত ভিন্ন হয় (যেমন $F = -k x^3$), তবে গতিটি পর্যাবৃত্ত হবে ঠিকই কিন্তু সরল ছন্দিত হবে না, কারণ এর ত্বরণ সরণের সাথে রৈখিকভাবে সম্পর্কিত নয় এবং এর পর্যায়কাল বিস্তারের ওপর নির্ভর করে। অতএব SHM হওয়ার জন্য বল অপেক্ষকে $F \propto -x$ কঠোরভাবে প্রযোজ্য হতে হয়।</t>
@@ -1405,11 +1375,6 @@
           <t>একটি কণার সরণ $x(t) = 3\sin(\omega t) + 4\cos(\omega t)$ দ্বারা প্রদত্ত। গতিটি কি সরল ছন্দিত স্পন্দন? এর বিস্তার $A$ এবং প্রারম্ভিক দশা কোণ $\phi$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>সমীকরণটিকে সাধারণ রূপ $x(t) = A\sin(\omega t + \phi) = A\sin(\omega t)\cos\phi + A\cos(\omega t)\sin\phi$-এর সাথে তুলনা করি। সহগ সমতা করে: $A\cos\phi = 3$ এবং $A\sin\phi = 4$। উভয় পাশে বর্গ করে যোগ করলে: $A^2(\cos^2\phi + \sin^2\phi) = 3^2 + 4^2 = 9 + 16 = 25 \implies A = 5\text{ m}$। ভাগ করে দশা কোণ: $\tan\phi = \frac{4}{3} \implies \phi = \tan^{-1}\left(\frac{4}{3}\right) \approx 53.13^\circ$। যেহেতু এটি একক কৌণিক কম্পাঙ্ক $\omega$ বিশিষ্ট একটি সাইনুসয়ডাল তরঙ্গ $x(t) = 5\sin(\omega t + 53.13^\circ)$, সেহেতু গতিটি একটি নিখুঁত সরল ছন্দিত স্পন্দন।</t>
@@ -1455,11 +1420,6 @@
           <t>একটি সুষম রডের দৈর্ঘ্য $L$, প্রস্থচ্ছেদ $A$ এবং উপাদানের ঘনত্ব $\rho$। রডটির প্রান্তীয় অনুদৈর্ঘ্য কম্পনের ক্ষেত্রে কার্যকর বল ধ্রুবক $k$ তার জ্যামিতিক মাত্রার ওপর কীভাবে নির্ভর করে?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>ইয়ং-এর গুণাঙ্কের সংজ্ঞা $Y = \frac{F/A}{\Delta L/L} \implies F = \left(\frac{YA}{L}\right)\Delta L$। হুকের সূত্রের প্রত্যয়নী বল $F = -k x$ এর সাথে তুলনা করলে কার্যকর বল ধ্রুবক পাওয়া যায় $k = \frac{YA}{L}$। অতএব বল ধ্রুবক প্রস্থচ্ছেদের ক্ষেত্রফলের সমানুপাতিক ($k \propto A$) এবং দৈর্ঘ্যের ব্যস্তানুপাতিক ($k \propto 1/L$)। রডটির ভর $M = \rho A L$। অনুদৈর্ঘ্য কম্পনের প্রাকৃতিক কম্পাঙ্ক $\omega \approx \sqrt{\frac{k}{M/3}} \propto \sqrt{\frac{YA/L}{\rho A L}} = \frac{1}{L}\sqrt{\frac{Y}{\rho}}$, যা প্রমাণ করে যে কম্পাঙ্ক রডের দৈর্ঘ্যের ব্যস্তানুপাতিক এবং প্রস্থচ্ছেদের ক্ষেত্রফলের ওপর স্বাধীন।</t>
@@ -1505,11 +1465,6 @@
           <t>একটি কণা $R$ ব্যাসার্ধের বৃত্তাকার পথে সমকৌণিক দ্রুতি $\omega$-তে ঘড়ির কাঁটার বিপরীত দিকে ঘুরছে। বৃত্তের ব্যাসের ওপর কণার লম্ব অভিক্ষেপের (Projection) গতি কি সরল ছন্দিত গতি? কণার অবস্থান, বেগ ও ত্বরণের অভিক্ষেপ বিশ্লেষণ কর।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>বৃত্তের কেন্দ্রকে মূলবিন্দু ধরলে যেকোনো সময় $t$-তে কণার অবস্থান ভেক্টর $\vec{r} = R\cos(\omega t + \phi)\hat{i} + R\sin(\omega t + \phi)\hat{j}$। $x$-অক্ষের (একটি ব্যাস) ওপর কণার অবস্থান হলো অভিক্ষেপ $x(t) = R\cos(\omega t + \phi)$। এর দ্বিতীয় সময় অন্তরক: $\ddot{x}(t) = -\omega^2 R\cos(\omega t + \phi) = -\omega^2 x(t)$। যেহেতু $\ddot{x} = -\omega^2 x$, এটি নিখুঁত সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণকে সিদ্ধ করে। বৃত্তাকার গতির কেন্দ্রমুখী ত্বরণ $\vec{a} = -\omega^2\vec{r}$-এর $x$-অক্ষ বরাবর উপাংশই হলো সরল ছন্দিত কণার ত্বরণ $-\omega^2 x$। অতএব সমবৃত্তীয় গতির যে কোনো ব্যাসের ওপর অভিক্ষেপ সর্বদা একটি নিখুঁত সরল ছন্দিত স্পন্দন।</t>
@@ -1555,11 +1510,6 @@
           <t>একটি কণা $A$ বিস্তার নিয়ে সরল ছন্দিত গতিতে দুলছে। সাম্যাবস্থা থেকে কত দূরত্বে কণাটির গতিশক্তি ও বিভব শক্তি সমান হবে এবং কোন অবস্থানে গতিশক্তি মোট শক্তির ৭৫% হবে?</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>মোট যান্ত্রিক শক্তি $E = \frac{1}{2}m\omega^2 A^2$। যে কোনো অবস্থান $x$-এ গতিশক্তি $K(x) = \frac{1}{2}m\omega^2 (A^2 - x^2)$ এবং বিভব শক্তি $U(x) = \frac{1}{2}m\omega^2 x^2$। (১) সমতার শর্ত $K = U \implies \frac{1}{2}m\omega^2(A^2 - x^2) = \frac{1}{2}m\omega^2 x^2 \implies A^2 - x^2 = x^2 \implies 2x^2 = A^2 \implies x = \pm \frac{A}{\sqrt{2}} \approx \pm 0.707 A$। (২) গতিশক্তি মোট শক্তির ৭৫% ($K = \frac{3}{4}E$): $\frac{1}{2}m\omega^2(A^2 - x^2) = \frac{3}{4}\left(\frac{1}{2}m\omega^2 A^2\right) \implies A^2 - x^2 = \frac{3}{4}A^2 \implies x^2 = \frac{1}{4}A^2 \implies x = \pm \frac{A}{2}$।</t>
@@ -1605,11 +1555,6 @@
           <t>একটি পূর্ণ পর্যায়কালে সরল ছন্দিত স্পন্দনরত কণার সময়ের সাপেক্ষে গড় গতিশক্তি $\langle K \rangle_t$ এবং গড় বিভব শক্তি $\langle U \rangle_t$ নির্ণয় কর এবং প্রমাণ কর যে তারা সমান ও মোট শক্তির অর্ধেক।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>সরণ $x(t) = A\sin(\omega t)$ এবং বেগ $v(t) = A\omega\cos(\omega t)$। গতিশক্তি $K(t) = \frac{1}{2}m A^2\omega^2\cos^2(\omega t)$ এবং বিভব শক্তি $U(t) = \frac{1}{2}m A^2\omega^2\sin^2(\omega t)$। সময়ের সাপেক্ষে গড় মান: $\langle \cos^2(\omega t) \rangle_t = \frac{1}{T}\int_0^T \cos^2(\omega t)dt = \frac{1}{2}$ এবং $\langle \sin^2(\omega t) \rangle_t = \frac{1}{T}\int_0^T \sin^2(\omega t)dt = \frac{1}{2}$। অতএব সময়ের সাপেক্ষে গড় গতিশক্তি $\langle K \rangle_t = \frac{1}{2}\left(\frac{1}{2}m\omega^2 A^2\right) = \frac{1}{4}m\omega^2 A^2 = \frac{E}{2}$। একইভাবে গড় বিভব শক্তি $\langle U \rangle_t = \frac{1}{2}\left(\frac{1}{2}m\omega^2 A^2\right) = \frac{1}{4}m\omega^2 A^2 = \frac{E}{2}$। ফলে সময়ের সাপেক্ষে $\langle K \rangle_t = \langle U \rangle_t = \frac{1}{2}E$।</t>
@@ -1655,11 +1600,6 @@
           <t>সাম্যাবস্থা থেকে চরম বিস্তার পর্যন্ত দূরত্বের ($x$) সাপেক্ষে গড় গতিশক্তি $\langle K \rangle_x$ এবং গড় বিভব শক্তি $\langle U \rangle_x$ নির্ণয় কর। সময়ের গড়ের সাথে এর অমিলের কারণ কী?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>দূরত্বের সাপেক্ষে গড় বিভব শক্তি: $\langle U \rangle_x = \frac{1}{A}\int_0^A U(x)dx = \frac{1}{A}\int_0^A \frac{1}{2}m\omega^2 x^2 dx = \frac{m\omega^2}{2A}\left[\frac{A^3}{3}\right] = \frac{1}{6}m\omega^2 A^2 = \frac{1}{3}E$। দূরত্বের সাপেক্ষে গড় গতিশক্তি: $\langle K \rangle_x = \frac{1}{A}\int_0^A \frac{1}{2}m\omega^2(A^2 - x^2)dx = \frac{m\omega^2}{2A}\left[A^3 - \frac{A^3}{3}\right] = \frac{1}{3}m\omega^2 A^2 = \frac{2}{3}E$। অনুপাত $\frac{\langle K \rangle_x}{\langle U \rangle_x} = \frac{2/3 E}{1/3 E} = 2:1$। অমিলের কারণ: কণাটি সাম্যাবস্থার কাছাকাছি অঞ্চলে দ্রুত বেগে অতিক্রম করে (অল্প সময় ব্যয় করে) কিন্তু চরম প্রান্তের কাছাকাছি মন্থর গতিতে বেশি সময় অতিবাহিত করে। ফলে স্থানিক সমবন্টনে সাম্যাবস্থার উচ্চ গতিশক্তি অঞ্চল কম প্রতিফলিত হয়, কিন্তু সময়িক সমবন্টনে তা নিখুঁত সমান থাকে।</t>
@@ -1703,11 +1643,6 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>একটি কণা $f$ কম্পাঙ্কে সরল ছন্দিত গতিতে স্পন্দিত হলে তার গতিশক্তি ও বিভব শক্তি কত কম্পাঙ্কে স্পন্দিত হবে? গাণিতিকভাবে প্রমাণ কর।</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1852,11 +1787,6 @@
           <t>$k$ স্প্রিং ধ্রুবকের একটি স্প্রিংয়ের সাথে যুক্ত $m$ ভরের ব্লক $A$ বিস্তার নিয়ে মসৃণ তলে দুলছে। ব্লকটি যখন সাম্যাবস্থা অতিক্রম করছিল, তখন স্প্রিংটিকে ঠিক মাঝখান থেকে কেটে অর্ধেক অংশ সরিয়ে ফেলা হলো। নতুন দোলনের বিস্তার $A'$ এবং কম্পাঙ্ক $\omega'$ কত?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>স্প্রিং কেটে অর্ধেক করলে তার স্প্রিং ধ্রুবক দ্বিগুণ হয়: $k' = 2k$। ফলে নতুন কৌণিক কম্পাঙ্ক $\omega' = \sqrt{\frac{k'}{m}} = \sqrt{\frac{2k}{m}} = \sqrt{2}\omega$। সাম্যাবস্থায় কণার বেগ সর্বোচ্চ থাকে: $v_{\max} = \omega A$। স্প্রিংয়ের অর্ধেক সরিয়ে ফেলার ঠিক মুহূর্তে ব্লকের তাৎক্ষণিক অবস্থান $x=0$ এবং বেগ $v_{\max}$ অপরিবর্তিত থাকে। নতুন বিস্তার $A'$ নির্ধারিত হয় নতুন কম্পাঙ্কের অধীনে ওই বেগের মাধ্যমে: $v_{\max} = \omega' A' \implies \omega A = (\sqrt{2}\omega) A' \implies A' = \frac{A}{\sqrt{2}}$। সাম্যাবস্থায় স্প্রিং বিভব শক্তি শূন্য থাকায় কোনো তাৎক্ষণিক শক্তি নষ্ট হয় না, কিন্তু পরবর্তীতে নতুন বিস্তার $A/\sqrt{2}$-এ নেমে আসে।</t>
@@ -1902,11 +1832,6 @@
           <t>$m$ ভরের একটি ব্লক $k$ স্প্রিংয়ে $A$ বিস্তার নিয়ে দুলছে। ব্লকটি যখন তার সর্বোচ্চ বিস্তারে ক্ষণিকের জন্য স্থির হলো, তখন তার ওপর আলতো করে সমান ভর $m$-এর অপর একটি ব্লক স্থাপন করা হলো যাতে তারা একসাথে জোড়া লেগে যায়। নতুন বিস্তার ও পর্যায়কাল কত?</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>সর্বোচ্চ বিস্তারে কণার বেগ শূন্য ($v=0$), ফলে কণার ভরবেগ শূন্য। অতিরিক্ত ভর স্থাপন করায় কোনো গতিশক্তি বিনষ্ট হয় না কারণ ওই মুহূর্তে সমস্ত শক্তি স্প্রিংয়ের বিভব শক্তিতে সঞ্চিত: $E = \frac{1}{2}k A^2$। স্প্রিংয়ের বিস্তার অপরিবর্তিত থাকে: $A' = A$। কিন্তু যৌথ ব্লকের মোট ভর দ্বিগুণ হয়: $M = 2m$। নতুন কৌণিক কম্পাঙ্ক $\omega' = \sqrt{\frac{k}{2m}} = \frac{\omega}{\sqrt{2}}$। ফলে নতুন পর্যায়কাল $T' = 2\pi\sqrt{\frac{2m}{k}} = \sqrt{2}T$। গতিশক্তি বিস্তার একই থাকে কিন্তু সর্বোচ্চ বেগ কমে $v'_{\max} = \omega' A = \frac{v_{\max}}{\sqrt{2}}$ হয়।</t>
@@ -1952,11 +1877,6 @@
           <t>আগের ব্যবস্থায় দ্বিতীয় ভর $m$ যদি সর্বোচ্চ বিস্তারে না ফেলে ব্লকটি যখন সাম্যাবস্থা অতিক্রম করছিল ($v = v_{\max}$) তখন উল্লম্বভাবে ফেলে আটকে দেওয়া হয়, তবে নতুন বিস্তার $A'$ এবং শক্তিক্ষয় কত হবে?</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>সাম্যাবস্থায় অনুভূমিক ভরবেগ সংরক্ষিত: $m v_{\max} = (m + m)V \implies V = \frac{v_{\max}}{2} = \frac{\omega A}{2}$। নতুন কৌণিক কম্পাঙ্ক $\omega' = \sqrt{\frac{k}{2m}} = \frac{\omega}{\sqrt{2}}$। সাম্যাবস্থায় নতুন বেগই হলো নতুন সর্বোচ্চ বেগ: $V = \omega' A' \implies \frac{\omega A}{2} = \left(\frac{\omega}{\sqrt{2}}\right)A' \implies A' = \frac{A}{\sqrt{2}}$। আদি মোট শক্তি $E_i = \frac{1}{2}m v_{\max}^2 = \frac{1}{2}k A^2$। চূড়ান্ত মোট শক্তি $E_f = \frac{1}{2}(2m)V^2 = m \left(\frac{v_{\max}}{2}\right)^2 = \frac{1}{4}m v_{\max}^2 = \frac{E_i}{2}$। অস্থিতিস্থাপক সংঘাতের কারণে ৫০% শক্তি তাপে নষ্ট হয় এবং বিস্তার কমে $A/\sqrt{2}$ হয়।</t>
@@ -2002,11 +1922,6 @@
           <t>একটি উল্লম্ব স্প্রিং-ব্লক সিস্টেমে অভিকর্ষের উপস্থিতিতে দোলনের সমীকরণ গঠন কর এবং প্রমাণ কর যে সাম্যাবস্থা স্থানান্তরিত হলেও অভিকর্ষের উপস্থিতি কার্যকর স্প্রিং ধ্রুবক বা দোলনের কম্পাঙ্ক পরিবর্তন করতে পারে না।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>অপ্রসারিত স্প্রিংয়ের অবস্থানকে মূলবিন্দু ধরলে সাম্যাবস্থায় ওজন স্প্রিং বলের সমান: $k x_0 = mg \implies x_0 = \frac{mg}{k}$। সাম্যাবস্থা থেকে অতিরিক্ত সরণ $y$ হলে মোট বল: $F_{\text{net}} = mg - k(x_0 + y) = mg - k x_0 - k y = -k y$। গতির সমীকরণ: $m \ddot{y} = -ky \implies \ddot{y} + \frac{k}{m}y = 0$। মোট শক্তি সাম্যাবস্থার সাপেক্ষে প্রকাশ করলে: $E = \frac{1}{2}m \dot{y}^2 + \frac{1}{2}k y^2 + \text{ধ্রুবক}$। এটি প্রমাণ করে যে অভিকর্ষ কেবল সাম্যাবস্থাকে $x_0 = \frac{mg}{k}$ নিচে স্থানান্তরিত করে, কিন্তু সিস্টেমের প্রত্যয়নী বলের ঢাল ($k$) বা কৌণিক কম্পাঙ্ক $\omega = \sqrt{k/m}$ বিন্দুমাত্র পরিবর্তন করে না।</t>
@@ -2052,11 +1967,6 @@
           <t>$L$ দৈর্ঘ্যের সরল দোলকের ক্ষেত্রে নিউটনের দ্বিতীয় সূত্র থেকে কৌণিক গতির নির্ভুল সমীকরণ $\frac{d^2\theta}{dt^2} + \frac{g}{L}\sin\theta = 0$ প্রতিপাদন কর এবং কেন $\theta \le 4^\circ$-এর জন্য এটিকে সরল ছন্দিত গতি ধরা যায়?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>ববের ভর $m$। বৃত্তাকার গতিপথের স্পর্শক বরাবর ক্রিয়াশীল ওজনের উপাংশ $F_t = -mg\sin\theta$ (ঋণাত্মক চিহ্ন সাম্যাবস্থা অভিমুখী প্রত্যয়নী বল নির্দেশ করে)। স্পর্শকীয় ত্বরণ $a_t = L\alpha = L\frac{d^2\theta}{dt^2}$। নিউটনের গতির সূত্র: $m a_t = F_t \implies m L \frac{d^2\theta}{dt^2} = -mg\sin\theta \implies \frac{d^2\theta}{dt^2} + \frac{g}{L}\sin\theta = 0$। সাইন অপেক্ষকের টেলর ধারা: $\sin\theta = \theta - \frac{\theta^3}{6} + \frac{\theta^5}{120} - \dots$। যদি কোণ খুব ক্ষুদ্র হয় ($\theta \le 4^\circ \approx 0.07\text{ rad}$), তবে $\frac{\theta^3}{6} \le \frac{(0.07)^3}{6} \approx 0.000057$, যার ফলে ত্রুটি $০.১\%$-এরও কম থাকে এবং $\sin\theta \approx \theta$ ধরা যায়। সমীকরণটি দাঁড়ায় $\ddot{\theta} + \omega^2\theta = 0$, যা সরল ছন্দিত গতির সমীকরণ নির্দেশ করে এবং $T = 2\pi\sqrt{L/g}$।</t>
@@ -2153,11 +2063,6 @@
           <t>একটি সরল দোলকের দৈর্ঘ্য পৃথিবীর ব্যাসার্ধ $R$-এর তুলনায় নগণ্য না হলে পর্যায়কালের সার্বজনীন সূত্র $T = 2\pi\sqrt{\frac{1}{g(1/L + 1/R)}}$। $L \to \infty$ হলে পর্যায়কাল কত হবে?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>যখন দোলকের দৈর্ঘ্য অত্যন্ত দীর্ঘ হয়, তখন সুতার ঝুলন বিন্দু পৃথিবীর কেন্দ্রাভিমুখী উল্লম্ব অভিকর্ষ রেখার সাথে সমান্তরাল থাকে না। কার্যকর প্রত্যয়নী বল উভয় কোণের সমষ্টি দ্বারা গঠিত হয়: $F = -mg(\theta + \phi) = -mg\left(\frac{x}{L} + \frac{x}{R}\right) = -mg x\left(\frac{1}{L} + \frac{1}{R}\right)$। ফলে কৌণিক কম্পাঙ্ক $\omega = \sqrt{g\left(\frac{1}{L} + \frac{1}{R}\right)}$ এবং পর্যায়কাল $T = 2\pi\sqrt{\frac{1}{g(1/L + 1/R)}}$। যখন দৈর্ঘ্য অসীম করা হয় ($L \to \infty \implies 1/L \to 0$), তখন পর্যায়কাল একটি সসীম সীমান্ত মানে পৌঁছায়: $T_{\max} = 2\pi\sqrt{\frac{R}{g}} \approx 2\pi\sqrt{\frac{6.4 \times 10^6}{9.8}} \approx 84.6\text{ minutes}$। এটি পৃথিবীর সুড়ঙ্গে পতনের পর্যায়কাল এবং ভূ-পৃষ্ঠের নিকটবর্তী উপগ্রহের পর্যায়কালের হুবহু সমান।</t>
@@ -2203,11 +2108,6 @@
           <t>একটি সরল দোলক (ক) $a$ সমত্বরণে অনুভূমিকভাবে চলমান ট্রলি এবং (খ) $\theta$ নতি কোণের ঘর্ষণহীন হেলানো তল বরাবর মুক্তভাবে পিছলে নামা ব্লকের ভেতর দুলছে। উভয় ক্ষেত্রে কার্যকর পর্যায়কাল কত?</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>কার্যকর মহাকর্ষীয় ত্বরণ $\vec{g}_{\text{eff}} = \vec{g} - \vec{a}$। (ক) অনুভূমিক ত্বরান্বিত ট্রলিতে: ছদ্ম ত্বরণ $-a\hat{i}$ এবং অভিকর্ষ $-g\hat{j}$ পরস্পর সমকোণে থাকে। কার্যকর ত্বরণের মান $g_{\text{eff}} = \sqrt{g^2 + a^2}$। পর্যায়কাল $T_1 = 2\pi\sqrt{\frac{L}{\sqrt{g^2 + a^2}}}$। (খ) হেলানো তলে মুক্ত পতনশীল ব্লকে: ব্লকের ত্বরণ $a = g\sin\theta$ তল বরাবর। তলের সমান্তরাল ত্বরণ $g\sin\theta - a = 0$। তলের লম্ব বরাবর ত্বরণ $g\cos\theta$। অতএব কার্যকর ত্বরণ কেবল তলের লম্ব উপাংশ: $g_{\text{eff}} = g\cos\theta$। পর্যায়কাল $T_2 = 2\pi\sqrt{\frac{L}{g\cos\theta}}$।</t>
@@ -2253,11 +2153,6 @@
           <t>একটি সরল দোলকের বব হিসেবে একটি ফাঁপা ধাতব গোলক ব্যবহার করা হলো যার তলদেশে একটি ক্ষুদ্র ছিদ্র আছে। গোলকটি সম্পূর্ণ জলপূর্ণ করে দুলিয়ে দিলে জল ধীরে ধীরে পড়ার সাথে সাথে পর্যায়কাল কীভাবে পরিবর্তিত হবে?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>সরল দোলকের কার্যকর দৈর্ঘ্য $L$ হলো ঝুলন বিন্দু থেকে ববের সামগ্রিক ভরকেন্দ্র (Center of Mass) পর্যন্ত দূরত্ব। (১) শুরুতে গোলকটি জলপূর্ণ থাকলে ভরকেন্দ্র গোলকের জ্যামিতিক কেন্দ্রে থাকে এবং পর্যায়কাল $T_0$। (২) জল যখন নিচের ছিদ্র দিয়ে বের হতে শুরু করে, তখন অবশিষ্ট জলের ভরকেন্দ্র নিচের দিকে নামতে থাকে। ফলে দোলকের কার্যকর দৈর্ঘ্য $L$ বৃদ্ধি পায় এবং পর্যায়কাল $T = 2\pi\sqrt{L/g}$ বৃদ্ধি পেতে থাকে। (৩) জল অর্ধেকের বেশি খালি হওয়ার পর ভরকেন্দ্র পুনরায় উপরের দিকে উঠতে শুরু করে এবং যখন গোলকটি সম্পূর্ণ খালি হয়ে যায়, তখন ভরকেন্দ্র পুনরায় ফাঁপা গোলকের জ্যামিতিক কেন্দ্রে ফিরে আসে। ফলে পর্যায়কাল হ্রাস পেয়ে ঠিক আদি মান $T_0$-তে ফিরে আসে। অতএব পর্যায়কাল প্রথমে বৃদ্ধি পায় এবং পরবর্তীতে হ্রাস পেয়ে পূর্বের মানে পৌঁছায়।</t>
@@ -2303,11 +2198,6 @@
           <t>একটি পেন্ডুলাম ঘড়ির ধাতব দণ্ডের রৈখিক প্রসারণ সহগ $\alpha$। তাপমাত্রা $\Delta \theta$ বৃদ্ধি পেলে ঘড়িটি প্রতিদিন কত সময় ধীরে চলবে (Time Lost per Day)?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>দোলকের পর্যায়কাল $T = 2\pi\sqrt{\frac{L}{g}} \propto L^{1/2}$। তাপমাত্রায় দৈর্ঘ্য বৃদ্ধি $L' = L(1 + \alpha \Delta\theta)$। পর্যায়কালের আপেক্ষিক পরিবর্তন ব্যবকলনে: $\frac{\Delta T}{T} = \frac{1}{2}\frac{\Delta L}{L} = \frac{1}{2}\alpha \Delta\theta$। একদিনে মোট সময় $T_0 = 86400\text{ s}$। যেহেতু পর্যায়কাল বৃদ্ধি পায়, ঘড়িটি ধীরে চলে। একদিনে সময় হারানোর পরিমাণ: $\Delta t = T_0 \frac{\Delta T}{T} = 86400 \times \left(\frac{1}{2}\alpha \Delta\theta\right) = 43200 \alpha \Delta\theta\text{ seconds}$।</t>
@@ -2353,11 +2243,6 @@
           <t>$L$ দৈর্ঘ্যের সরল দোলকের $m$ ভরের ববে $+q$ আধান আছে। পুরো ব্যবস্থাটিতে (ক) খাড়া নিম্নমুখী এবং (খ) অনুভূমিক অভিমুখে $E$ সুষম বৈদ্যুতিক ক্ষেত্র প্রয়োগ করলে পর্যায়কাল কত হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>(ক) খাড়া নিম্নমুখী বৈদ্যুতিক ক্ষেত্রে: বৈদ্যুতিক বল $qE$ নিচের দিকে কাজ করে। কার্যকর ত্বরণ $g_{\text{eff}} = g + \frac{qE}{m}$। পর্যায়কাল $T_1 = 2\pi\sqrt{\frac{L}{g + qE/m}}$। (ক্ষেত্র ঊর্ধ্বমুখী হলে $g_{\text{eff}} = g - qE/m$ হতো)। (খ) অনুভূমিক বৈদ্যুতিক ক্ষেত্রে: অনুভূমিক বল $qE$ এবং উল্লম্ব ওজন $mg$ সমকোণে কাজ করে। কার্যকর ত্বরণ $g_{\text{eff}} = \sqrt{g^2 + (qE/m)^2}$। নতুন সাম্যাবস্থা উল্লম্বের সাথে $\tan\theta = \frac{qE}{mg}$ কোণে হেলে থাকবে এবং পর্যায়কাল $T_2 = 2\pi\sqrt{\frac{L}{\sqrt{g^2 + (qE/m)^2}}}$।</t>
@@ -2403,11 +2288,6 @@
           <t>$L$ দৈর্ঘ্যের একটি সরল দোলকের ঝুলন বিন্দুর ঠিক উল্লম্ব রেখা বরাবর $L/2$ গভীরতায় একটি শক্ত পেরেক বা পিন পোঁতা আছে। দোলকটিকে ক্ষুদ্র বিস্তারে দুলিয়ে দিলে এর পূর্ণ পর্যায়কাল কত হবে?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>দোলকটি যখন পেরেকের বিপরীত দিকে (বামপাশে) দুলবে, তখন তার কার্যকর দৈর্ঘ্য থাকে সম্পূর্ণ $L$ এবং এই অংশের দোলনে সময় লাগে একটি পূর্ণ দোলনের অর্ধেক: $t_1 = \frac{1}{2}\left(2\pi\sqrt{\frac{L}{g}}\right) = \pi\sqrt{\frac{L}{g}}$। যখন দোলকটি পেরেকের দিকে (ডানপাশে) যায়, তখন সুতাটি পেরেকের সাথে আটকে যায় এবং অবশিষ্ট মুক্ত দৈর্ঘ্য দাঁড়ায় $L - L/2 = L/2$। ফলে ডানপাশের অর্ধ-দোলনে সময় লাগে: $t_2 = \frac{1}{2}\left(2\pi\sqrt{\frac{L/2}{g}}\right) = \pi\sqrt{\frac{L}{2g}}$। অতএব সম্পূর্ণ এক চক্রের মোট পর্যায়কাল: $T = t_1 + t_2 = \pi\sqrt{\frac{L}{g}} + \pi\sqrt{\frac{L}{2g}} = \pi\sqrt{\frac{L}{g}}\left(1 + \frac{1}{\sqrt{2}}\right)$।</t>
@@ -2453,11 +2333,6 @@
           <t>একটি সরল দোলক তরলে দুলছে যেখানে সান্দ্র ড্র্যাগ বল $F = -b v$। দোলকের কৌণিক বিস্তার $N$ টি পূর্ণ দোলনের পর আদি মানের $1/e$ অংশে নেমে আসলে দোলকটির গুণমান গুণক (Quality Factor $Q$) নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>অবমন্দিত দোলনের বিস্তার সমীকরণ: $\theta(t) = \theta_0 e^{-\gamma t}$, যেখানে $\gamma = \frac{b}{2m}$। $N$ টি দোলনের সময় $t = N T$। শর্তানুসারে $e^{-\gamma N T} = e^{-1} \implies \gamma N T = 1 \implies \gamma T = \frac{1}{N}$। লগারিদমিক হ্রাস (Logarithmic Decrement) $\delta = \gamma T = \frac{1}{N}$। কোয়ালিটি ফ্যাক্টরের সংজ্ঞা $Q = \frac{\omega_0}{2\gamma} = \frac{2\pi/T}{2\gamma} = \frac{\pi}{\gamma T} = \frac{\pi}{\delta}$। মান বসিয়ে পাই: $Q = \pi N$। অতএব বিস্তার $1/e$ হতে প্রয়োজনীয় দোলন সংখ্যার $\pi$ গুণ হলো তার কোয়ালিটি ফ্যাক্টর।</t>
@@ -2503,11 +2378,6 @@
           <t>একই $L$ দৈর্ঘ্যের সুতায় বাঁধা সমান ভরের দুটি ববের একটি উল্লম্ব সমতলে সরল দোলক হিসেবে দুলছে ($T_s$) এবং অপরটি উল্লম্বের সাথে $\theta$ কোণে অনুভূমিক বৃত্তে কনিক্যাল পেন্ডুলাম হিসেবে ঘুরছে ($T_c$)। তাদের পর্যায়কালের অনুপাত কত?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>সরল দোলকের পর্যায়কাল $T_s = 2\pi\sqrt{\frac{L}{g}}$। কনিক্যাল পেন্ডুলামে সুতার টান $T\cos\theta = mg$ এবং অনুভূমিক কেন্দ্রমুখী বল $T\sin\theta = m\omega^2(L\sin\theta) \implies \omega^2 = \frac{g}{L\cos\theta}$। ফলে কনিক্যাল পেন্ডুলামের পর্যায়কাল $T_c = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{L\cos\theta}{g}}$। তাদের অনুপাত: $\frac{T_c}{T_s} = \frac{2\pi\sqrt{\frac{L\cos\theta}{g}}}{2\pi\sqrt{\frac{L}{g}}} = \sqrt{\cos\theta}$। যেহেতু যে কোনো বাস্তব কোণে $\cos\theta &lt; 1$, সেহেতু $T_c &lt; T_s$ সর্বদা। কোণ $\theta = 60^\circ$ হলে $T_c = T_s\sqrt{1/2} = \frac{T_s}{\sqrt{2}}$।</t>
@@ -2553,11 +2423,6 @@
           <t>একটি অনড় বস্তুর ভর $M$ এবং ভরকেন্দ্রগামী অক্ষের সাপেক্ষে চক্রগতির ব্যাসার্ধ $k$। ভরকেন্দ্র থেকে $l$ দূরত্বে অবস্থিত একটি অনুভূমিক মসৃণ অক্ষের সাপেক্ষে বস্তুটিকে ক্ষুদ্র কোণে দোলালে এর পর্যায়কাল $T = 2\pi\sqrt{\frac{k^2 + l^2}{gl}}$ প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>ঝুলন অক্ষের সাপেক্ষে বস্তুর সমান্তরাল অক্ষ উপপাদ্য অনুসারে জড়তার ভ্রামক $I = I_{\text{cm}} + M l^2 = M k^2 + M l^2 = M(k^2 + l^2)$। সাম্যাবস্থা থেকে $\theta$ কোণে বিচ্যুত করলে ওজনের প্রত্যয়নী টর্ক $\tau = -M g l \sin\theta \approx -M g l \theta$ (ক্ষুদ্র কোণে)। ঘূর্ণন গতির নিউটনীয় সমীকরণ: $I \ddot{\theta} = \tau \implies M(k^2 + l^2)\ddot{\theta} = -M g l \theta \implies \ddot{\theta} + \left(\frac{gl}{k^2 + l^2}\right)\theta = 0$। এটি কৌণিক সরল ছন্দিত স্পন্দন নির্দেশ করে যার কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{gl}{k^2 + l^2}}$। অতএব পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{k^2 + l^2}{gl}} = 2\pi\sqrt{\frac{L_{\text{eq}}}{g}}$, যেখানে তুল্য সরল দোলকের দৈর্ঘ্য $L_{\text{eq}} = l + \frac{k^2}{l}$।</t>
@@ -2603,11 +2468,6 @@
           <t>উপরের যৌগিক দোলকে ভরকেন্দ্র থেকে ঝুলন অক্ষের দূরত্ব $l$-এর কোন মানের জন্য পর্যায়কাল $T$ সর্বনিম্ন হবে এবং সেই সর্বনিম্ন পর্যায়কাল $T_{\min}$ নির্ণয় কর।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>পর্যায়কাল $T = 2\pi\sqrt{\frac{k^2 + l^2}{gl}}$। $T$ সর্বনিম্ন হবে যখন ভগ্নাংশ $f(l) = \frac{k^2 + l^2}{l} = \frac{k^2}{l} + l$ সর্বনিম্ন হয়। ব্যবকলন করি: $\frac{df}{dl} = -\frac{k^2}{l^2} + 1 = 0 \implies l^2 = k^2 \implies l = k$। দ্বিতীয় অন্তরক $\frac{d^2 f}{dl^2} = \frac{2k^2}{l^3} &gt; 0$, ফলে $l = k$-তে নূন্যতম মান ঘটে। অর্থাৎ ঝুলন অক্ষ ভরকেন্দ্র থেকে ঠিক চক্রগতির ব্যাসার্ধের সমান দূরত্বে থাকলে পর্যায়কাল সর্বনিম্ন হয়। ওই দূরত্বে তুল্য দৈর্ঘ্য $L_{\min} = k + \frac{k^2}{k} = 2k$। অতএব সর্বনিম্ন পর্যায়কাল $T_{\min} = 2\pi\sqrt{\frac{2k}{g}}$।</t>
@@ -2653,11 +2513,6 @@
           <t>যৌগিক দোলকের তুল্য সরল দোলকের দৈর্ঘ্য $L = l + l'$ (যেখানে $l' = k^2/l$)। প্রমাণ কর যে ঝুলন কেন্দ্র (Center of Suspension) এবং দোলন কেন্দ্র (Center of Oscillation) পরস্পরের সাথে সম্পূর্ণ বিনিময়যোগ্য (Interchangeable)।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>ভরকেন্দ্র থেকে $l$ দূরত্বে ঝুলন অক্ষ $S$ থাকলে পর্যায়কাল $T = 2\pi\sqrt{\frac{l + k^2/l}{g}}$। দোলন কেন্দ্র $O$ হলো ভরকেন্দ্রের অপর পাশে অবস্থিত একটি বিন্দু যার দূরত্ব $l' = \frac{k^2}{l}$। এখন বস্তুটিকে উল্টে দিয়ে যদি $O$ বিন্দু দিয়ে ঝুলিয়ে দেওয়া হয়, তবে ভরকেন্দ্র থেকে নতুন ঝুলন দূরত্ব হবে $l_{\text{new}} = l' = \frac{k^2}{l}$। নতুন তুল্য দৈর্ঘ্য $L' = l_{\text{new}} + \frac{k^2}{l_{\text{new}}} = l' + \frac{k^2}{k^2/l} = l' + l = L$। ফলে নতুন পর্যায়কাল $T' = 2\pi\sqrt{\frac{L'}{g}} = 2\pi\sqrt{\frac{L}{g}} = T$। অর্থাৎ ঝুলন বিন্দু এবং দোলন বিন্দু বিনিময় করলেও পর্যায়কাল নিখুঁতভাবে অপরিবর্তিত থাকে।</t>
@@ -2703,11 +2558,6 @@
           <t>কেটারের রিভার্সিবল পেন্ডুলামে দুটি বিপরীত ছুরিকাধার $S_1$ ও $S_2$ থাকে যাদের মধ্যবর্তী দূরত্ব $L$ অত্যন্ত সূক্ষ্মভাবে মাপা যায়। কেন এই পদ্ধতিতে ভরকেন্দ্রের অবস্থান বা জড়তার ভ্রামক না জেনেই অভিকর্ষজ ত্বরণ $g$ নিখুঁতভাবে পরিমাপ করা যায়?</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>পেন্ডুলামের সামঞ্জস্যযোগ্য ভরগুলো এমনভাবে স্থাপন করা হয় যাতে উভয় ছুরিকাধারের সাপেক্ষে দোলনের পর্যায়কাল সমান হয় ($T_1 = T_2 = T$)। বিনিময়যোগ্যতা উপপাদ্য অনুসারে যখন উভয় প্রান্তের পর্যায়কাল সমান হয়, তখন দুই ছুরিকাধারের মধ্যবর্তী জ্যামিতিক দূরত্ব $L$ ঠিক তুল্য সরল দোলকের দৈর্ঘ্যের সমান হয় ($L = l_1 + l_2$)। ফলে পর্যায়কালের সমীকরণ দাঁড়ায় $T = 2\pi\sqrt{\frac{L}{g}} \implies g = \frac{4\pi^2 L}{T^2}$। এখানে বস্তুর ভর $M$, ভরকেন্দ্রের দূরত্ব বা জড়তার ভ্রামক জানার কোনো প্রয়োজন হয় না; কেবল দুটি নাইফ-এজের মধ্যবর্তী সরল রৈখিক দূরত্ব $L$ এবং পর্যায়কাল $T$ অতি সূক্ষ্মভাবে মেপেই $g$-এর মান শতকরা ০.০০০১% পর্যন্ত নির্ভুলভাবে নির্ধারণ করা সম্ভব হয়।</t>
@@ -2753,11 +2603,6 @@
           <t>$L$ দৈর্ঘ্যের একটি সুষম সরু রড তার এক প্রান্তগামী অনুভূমিক অক্ষের সাপেক্ষে উল্লম্ব তলে দুলছে। রডটির দোলনের পর্যায়কাল $T$ এবং তুল্য সরল দোলকের দৈর্ঘ্য $L_{\text{eq}}$ কত?</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>এক প্রান্তের সাপেক্ষে রডের জড়তার ভ্রামক $I = \frac{1}{3}M L^2$। রডের ভরকেন্দ্র এক প্রান্ত থেকে মধ্যবিন্দুতে অবস্থিত, ফলে $l = \frac{L}{2}$। যৌগিক দোলকের সূত্র: $T = 2\pi\sqrt{\frac{I}{Mgl}} = 2\pi\sqrt{\frac{\frac{1}{3}ML^2}{Mg(L/2)}} = 2\pi\sqrt{\frac{2L}{3g}}$। তুল্য সরল দোলকের দৈর্ঘ্য $L_{\text{eq}} = \frac{2}{3}L$। অর্থাৎ $L$ দৈর্ঘ্যের সুষম রডের দোলনকাল $\frac{2}{3}L$ দৈর্ঘ্যের সাধারণ সরল দোলকের দোলনকালের সমান।</t>
@@ -2803,11 +2648,6 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি পাতলা সুষম বৃত্তাকার রিং তার পরিধির একটি বিন্দুগামী এবং রিংয়ের তলের লম্ব অনুভূমিক কীলকের সাপেক্ষে দুলছে। রিংটির দোলনের পর্যায়কাল কত?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>রিংয়ের কেন্দ্রগামী ও তলের লম্ব অক্ষের সাপেক্ষে জড়তার ভ্রামক $I_{\text{cm}} = M R^2$। সমান্তরাল অক্ষ উপপাদ্য অনুসারে পরিধির কীলক বিন্দুর সাপেক্ষে জড়তার ভ্রামক $I = I_{\text{cm}} + M R^2 = M R^2 + M R^2 = 2M R^2$। কীলক থেকে ভরকেন্দ্রের দূরত্ব $l = R$। পর্যায়কালের সমীকরণ: $T = 2\pi\sqrt{\frac{I}{Mgl}} = 2\pi\sqrt{\frac{2M R^2}{Mg R}} = 2\pi\sqrt{\frac{2R}{g}}$। তুল্য সরল দোলকের দৈর্ঘ্য $L_{\text{eq}} = 2R$ (রিংয়ের ব্যাসের সমান)।</t>
@@ -2853,11 +2693,6 @@
           <t>একটি তারের নিচের প্রান্তে $I$ জড়তার ভ্রামক বিশিষ্ট একটি অনড় বস্তু আটকানো। তারটির টরশনাল কাপল প্রতি একক রেডিয়ানে $C$। বস্তুটিকে সামান্য কোণে মোচড় দিয়ে ছেড়ে দিলে কৌণিক দোলনের সমীকরণ গঠন কর এবং পর্যায়কাল প্রতিপাদন কর।</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>বস্তুটিকে $\theta$ কোণে ঘোরালে তারের স্থিতিস্থাপক প্রত্যয়নী টর্ক $\tau = -C \theta$। ঘূর্ণন গতির সূত্রানুসারে $I \alpha = \tau \implies I \frac{d^2\theta}{dt^2} = -C \theta \implies \frac{d^2\theta}{dt^2} + \left(\frac{C}{I}\right)\theta = 0$। এটি একটি কৌণিক সরল ছন্দিত গতি যার কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{C}{I}}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = 2\pi\sqrt{\frac{I}{C}}$। লক্ষণীয় যে টরশন পেন্ডুলামের পর্যায়কাল মহাকর্ষীয় ত্বরণ $g$-এর ওপর সম্পূর্ণ স্বাধীন, ফলে এটি যেকোনো মহাকর্ষীয় ক্ষেত্রে বা মহাকাশে একই সময়কাল বজায় রাখে এবং মেকানিক্যাল ঘড়ির ব্যালেন্স হুইলে ব্যবহৃত হয়।</t>
@@ -2903,11 +2738,6 @@
           <t>$R$ ব্যাসার্ধ ও $M$ ভরের একটি সুষম নিরেট বৃত্তাকার ডিস্ক তার পরিধির কিনারায় একটি অনুভূমিক মসৃণ পেরেকের ওপর ঝুলছে এবং ডিস্কের তলে দুলছে। ডিস্কটির দোলনের পর্যায়কাল কত?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>ডিস্কের কেন্দ্রগামী তলের লম্ব অক্ষের সাপেক্ষে জড়তার ভ্রামক $I_{\text{cm}} = \frac{1}{2}M R^2$। সমান্তরাল অক্ষ উপপাদ্য অনুসারে পরিধির কিনারার বিন্দুর সাপেক্ষে জড়তার ভ্রামক $I = \frac{1}{2}M R^2 + M R^2 = \frac{3}{2}M R^2$। ঝুলন বিন্দু থেকে ভরকেন্দ্রের দূরত্ব $l = R$। পর্যায়কালের সমীকরণ: $T = 2\pi\sqrt{\frac{I}{Mgl}} = 2\pi\sqrt{\frac{\frac{3}{2}M R^2}{Mg R}} = 2\pi\sqrt{\frac{3R}{2g}}$। তুল্য দৈর্ঘ্য $L_{\text{eq}} = \frac{3}{2}R$।</t>
@@ -2953,11 +2783,6 @@
           <t>$L$ দৈর্ঘ্য ও $r$ ব্যাসার্ধের একটি ধাতব তারের প্রান্তে $I$ জড়তার ভ্রামক বিশিষ্ট ডিস্ক ঝুলিয়ে টরশন দোলনের পর্যায়কাল $T$ পাওয়া গেল। তারের উপাদানের ব্যবর্তন গুণাঙ্ক $\eta$ নির্ণয়ের সূত্র গঠন কর।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>সিলিন্ডারীয় তারের টরশনাল ধ্রুবক $C = \frac{\pi \eta r^4}{2L}$। টরশন পেন্ডুলামের পর্যায়কাল $T = 2\pi\sqrt{\frac{I}{C}} \implies T^2 = \frac{4\pi^2 I}{C}$। $C$-এর মান বসিয়ে পাই: $T^2 = \frac{4\pi^2 I}{\frac{\pi \eta r^4}{2L}} = \frac{8\pi I L}{\eta r^4}$। সমীকরণটি পুনর্বিন্যাস করে ব্যবর্তন গুণাঙ্ক পাওয়া যায়: $\eta = \frac{8\pi I L}{T^2 r^4}$। ব্যাসার্ধ $r$-এর ওপর চতুর্থ ঘাত নির্ভরতার কারণে তারের ব্যাসার্ধ অত্যন্ত সূক্ষ্মভাবে স্ক্রু-গেজ দ্বারা পরিমাপ করতে হয়।</t>
@@ -3003,11 +2828,6 @@
           <t>$h$ উচ্চতা বিশিষ্ট একটি সুষম সমদ্বিবাহু ত্রিভুজাকার পাতলা ফলক তার শীর্ষবিন্দুগামী অনুভূমিক অক্ষের সাপেক্ষে উল্লম্ব তলে দুলছে। দোলনের পর্যায়কাল কত?</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>শীর্ষবিন্দু থেকে ভরকেন্দ্রের দূরত্ব $l = \frac{2}{3}h$। শীর্ষবিন্দুগামী অনুভূমিক অক্ষের সাপেক্ষে ত্রিভুজের জড়তার ভ্রামক $I = \frac{1}{2}M h^2$। পর্যায়কালের সমীকরণ: $T = 2\pi\sqrt{\frac{I}{Mgl}} = 2\pi\sqrt{\frac{\frac{1}{2}M h^2}{Mg (2/3 h)}} = 2\pi\sqrt{\frac{3h}{4g}}$। তুল্য সরল দোলকের দৈর্ঘ্য $L_{\text{eq}} = \frac{3}{4}h$।</t>
@@ -3053,11 +2873,6 @@
           <t>$k_1$ ও $k_2$ স্প্রিং ধ্রুবকের দুটি স্প্রিং-এর সাথে $m$ ভরের একটি ব্লককে (ক) শ্রেণি সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করা হলো। উভয় ক্ষেত্রে ব্লকের দোলনের পর্যায়কালের অনুপাত $T_{\text{series}} : T_{\text{parallel}}$ কত?</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>(ক) শ্রেণি সমবায়ে তুল্য স্প্রিং ধ্রুবক $k_s = \frac{k_1 k_2}{k_1 + k_2}$। পর্যায়কাল $T_{\text{series}} = 2\pi\sqrt{\frac{m}{k_s}} = 2\pi\sqrt{\frac{m(k_1 + k_2)}{k_1 k_2}}$। (খ) সমান্তরাল সমবায়ে তুল্য স্প্রিং ধ্রুবক $k_p = k_1 + k_2$। পর্যায়কাল $T_{\text{parallel}} = 2\pi\sqrt{\frac{m}{k_p}} = 2\pi\sqrt{\frac{m}{k_1 + k_2}}$। পর্যায়কালের অনুপাত: $\frac{T_{\text{series}}}{T_{\text{parallel}}} = \frac{\sqrt{\frac{m(k_1 + k_2)}{k_1 k_2}}}{\sqrt{\frac{m}{k_1 + k_2}}} = \sqrt{\frac{(k_1 + k_2)^2}{k_1 k_2}} = \frac{k_1 + k_2}{\sqrt{k_1 k_2}}$। যদি $k_1 = k_2 = k$ হয়, তবে $\frac{T_{\text{series}}}{T_{\text{parallel}}} = \frac{2k}{k} = 2:1$।</t>
@@ -3101,11 +2916,6 @@
       <c r="G43" t="inlineStr">
         <is>
           <t>একটি অনুভূমিক মসৃণ মেঝের ওপর $m$ ভরের একটি ব্লকের বামপাশে $k_1$ স্প্রিং ধ্রুবকের স্প্রিং এবং ডানপাশে $k_2$ স্প্রিং ধ্রুবকের স্প্রিং দুটি অনড় দেয়ালের সাথে যুক্ত। সংস্থাটির কার্যকর স্প্রিং ধ্রুবক ও পর্যায়কাল কত?</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3201,11 +3011,6 @@
           <t>মসৃণ অনুভূমিক সমতলে $m_1$ ও $m_2$ ভরের দুটি ব্লক একটি $k$ স্প্রিং ধ্রুবকের স্প্রিং দ্বারা সংযুক্ত। বাহ্যিক কোনো অবলম্বন ছাড়া সংস্থাটিকে প্রসারিত করে ছেড়ে দিলে দোলনের পর্যায়কাল কত হবে?</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>সংস্থার ওপর অনুভূমিক কোনো বাহ্যিক বল নেই, ফলে ভরকেন্দ্র সর্বদা স্থির থাকে ($m_1 x_1 = m_2 x_2$)। আপেক্ষিক স্থানাঙ্ক $x = x_1 + x_2$। ব্লকের গতি সমীকরণ: $m_1 \ddot{x}_1 = -kx$ এবং $m_2 \ddot{x}_2 = -kx \implies \ddot{x}_1 = -\frac{kx}{m_1}$ এবং $\ddot{x}_2 = -\frac{kx}{m_2}$। যোগ করি: $\ddot{x} = \ddot{x}_1 + \ddot{x}_2 = -kx\left(\frac{1}{m_1} + \frac{1}{m_2}\right) = -\frac{k}{\mu}x$, যেখানে হ্রাসকৃত ভর (Reduced Mass) $\mu = \frac{m_1 m_2}{m_1 + m_2}$। এটি একটি একক ব্লকের সরল ছন্দিত গতির সমতুল্য। অতএব পর্যায়কাল $T = 2\pi\sqrt{\frac{\mu}{k}} = 2\pi\sqrt{\frac{m_1 m_2}{k(m_1 + m_2)}}$।</t>
@@ -3302,11 +3107,6 @@
           <t>$\alpha$ নতি কোণের একটি মসৃণ হেলানো তল বরাবর $k$ স্প্রিং ধ্রুবকের একটি স্প্রিং দ্বারা $m$ ভরের একটি ব্লক বাঁধা আছে। ব্লকের দোলনের পর্যায়কাল তলের নতি কোণ $\alpha$-এর ওপর নির্ভর করে কি?</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>হেলানো তল বরাবর ওজনের সমান্তরাল উপাংশ $mg\sin\alpha$। সাম্যাবস্থায় স্প্রিংটির প্রসারণ ঘটে $x_0 = \frac{mg\sin\alpha}{k}$। সাম্যাবস্থা থেকে অতিরিক্ত সরণ $x$ ঘটালে মোট প্রত্যয়নী বল $F_{\text{net}} = mg\sin\alpha - k(x_0 + x) = mg\sin\alpha - mg\sin\alpha - kx = -kx$। গতির সমীকরণ $m \ddot{x} + kx = 0$। পর্যায়কাল $T = 2\pi\sqrt{\frac{m}{k}}$। যেহেতু নতি কোণের পদ $mg\sin\alpha$ সাম্যাবস্থার স্থিতিস্থাপক টানের সাথে বাতিল হয়ে যায়, সেহেতু পর্যায়কাল নতি কোণ $\alpha$-এর ওপর সম্পূর্ণ স্বাধীন থাকে। অনুভূমিক সমতল, উল্লম্ব তল বা যে কোনো হেলানো তলে মসৃণ স্প্রিং-ব্লকের পর্যায়কাল অভিন্ন ($2\pi\sqrt{m/k}$) থাকে।</t>
@@ -3352,11 +3152,6 @@
           <t>মসৃণ মেঝের ওপর $M$ ভরের ব্লক রাখা যা $k$ স্প্রিং ধ্রুবকের স্প্রিং দ্বারা যুক্ত। তার ওপর $m$ ভরের একটি ছোট ব্লক রাখা যার সাথে $M$-এর স্থৈতিক ঘর্ষণ গুণাঙ্ক $\mu$। সংস্থাটি সরল ছন্দিত গতিতে দুললে উপরের ব্লকটি পিছলে না পড়ার জন্য সর্বোচ্চ বিস্তার $A_{\max}$ কত?</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>সংস্থার মোট ভর $M + m$। কৌণিক কম্পাঙ্ক $\omega = \sqrt{\frac{k}{M + m}}$। সর্বোচ্চ বিস্তারে সংস্থার ত্বরণ সর্বোচ্চ হয়: $a_{\max} = \omega^2 A = \frac{k A}{M + m}$। উপরের ব্লক $m$-কে এই ত্বরণে রাখার একমাত্র বল হলো উভয়ের মধ্যবর্তী স্থৈতিক ঘর্ষণ বল $f_s$। নিউটনের দ্বিতীয় সূত্র: $f_s = m a_{\max} = m \frac{k A}{M + m}$। পিছলানো না ঘটার শর্ত: $f_s \le f_{s,\max} = \mu mg \implies m \frac{k A}{M + m} \le \mu mg \implies \frac{k A}{M + m} \le \mu g \implies A \le \frac{\mu(M + m)g}{k}$। অতএব সর্বোচ্চ নিরাপদ বিস্তার $A_{\max} = \frac{\mu(M + m)g}{k}$।</t>
@@ -3400,11 +3195,6 @@
       <c r="G49" t="inlineStr">
         <is>
           <t>$k$ স্প্রিং ধ্রুবকের একটি স্প্রিং-কে $1:n$ দৈর্ঘ্যের অনুপাতে দুটি অংশে কাটা হলো। ছোট অংশের সাথে $m$ ভর যুক্ত করলে দোলনের কম্পাঙ্ক আদি কম্পাঙ্ক $f_0$-এর কত গুণ হবে?</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3499,11 +3289,6 @@
           <t>একটি মসৃণ অনুভূমিক রডে পরানো $m$ ভরের একটি কলার রড থেকে $h$ উল্লম্ব দূরত্বে অবস্থিত একটি বিন্দুতে আটকানো $k$ স্প্রিং ধ্রুবকের স্প্রিং (স্বাভাবিক অপ্রসারিত দৈর্ঘ্য $h$) দ্বারা যুক্ত। কলারটিকে সামান্য অনুভূমিক সরণ $x$ ($x \ll h$) ঘটালে এর দোলন কি সরল ছন্দিত হবে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>কলারটির সরণ $x$ হলে স্প্রিংয়ের নতুন দৈর্ঘ্য $L = \sqrt{h^2 + x^2}$। স্প্রিংয়ের প্রসারণ $\Delta L = \sqrt{h^2 + x^2} - h$। রড বরাবর প্রত্যয়নী বল হলো স্প্রিং বলের অনুভূমিক উপাংশ: $F_x = -k \Delta L \sin\theta = -k(\sqrt{h^2 + x^2} - h)\frac{x}{\sqrt{h^2 + x^2}} = -k x\left(1 - \frac{h}{\sqrt{h^2 + x^2}}\right) = -k x\left(1 - (1 + x^2/h^2)^{-1/2}\right)$। দ্বিপদী বিস্তার করি ($x \ll h$): $(1 + x^2/h^2)^{-1/2} \approx 1 - \frac{x^2}{2h^2}$। মান বসালে: $F_x \approx -k x\left[1 - \left(1 - \frac{x^2}{2h^2}\right)\right] = -\frac{k}{2h^2}x^3$। লক্ষণীয় যে বলটি সরণের প্রথম ঘাত নয় বরং ঘনকের সমানুপাতিক ($F \propto -x^3$)। ফলে রৈখিক প্রত্যয়নী বল অনুপস্থিত থাকায় গতিটি ক্ষুদ্র বিস্তারে সরল ছন্দিত গতি (SHM) নয় বরং একটি অ-রৈখিক এনহারমোনিক পর্যাবৃত্ত দোলন।</t>
@@ -3533,38 +3318,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত গতির সরণ ও বেগ (সমস্যা 1)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>[সমস্যা 1: সরল ছন্দিত গতির সরণ ও বেগ]
-একটি কণা $x(t) = 4 \sin(4\pi t + \frac{\pi}{5})\text{ cm}$ সমীকরণানুযায়ী সরল ছন্দিত স্পন্দনে গতিশীল। কণাটির বিস্তার, পর্যায়কাল, এবং $t = 0.5\text{ s}$-এ বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি সরল ছন্দিত স্পন্দনশীল কণার ব্যবকলনীয় সমীকরণ $4\frac{d^2x}{dt^2} + 100x = 0$। কণাটির কৌণিক কম্পাঙ্ক $\omega$, পর্যায়কাল $T$ এবং কম্পাঙ্ক $f$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 1)।</t>
+          <t>সমীকরণটিকে আদর্শ আকার $\frac{d^2x}{dt^2} + \omega^2 x = 0$-এ রূপান্তর করে: $\frac{d^2x}{dt^2} + 25x = 0 \implies \omega^2 = 25 \implies \omega = 5.0\text{ rad/s}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = \frac{2\pi}{5} \approx 1.257\text{ s}$। কম্পাঙ্ক $f = \frac{1}{T} = \frac{5}{2\pi} \approx 0.796\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>$\omega = 5.0\text{ rad/s}, T = 1.26\text{ s}, f = 0.796\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3584,7 +3369,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>স্প্রিং সমবায় ও তুল্য দোলনকাল (সমস্যা 2)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3597,30 +3382,26 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>[সমস্যা 2: স্প্রিং সমবায় ও তুল্য দোলনকাল]
-##PRESET:spring-mass[size:medium]##
-$k_1 = 600\text{ N/m}$ এবং $k_2 = 500\text{ N/m}$ স্প্রিং ধ্রুবকের দুটি স্প্রিংকে শ্রেণিতে এবং সমান্তরালে যুক্ত করে $M = 2\text{ kg}$ ভর ঝুলালে উভয় ক্ষেত্রে পর্যায়কাল কত হবে?</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি কণার সরল ছন্দিত গতির সমীকরণ $x(t) = 0.08\sin\left(10\pi t + rac{\pi}{4}+ight)\text{ m}$। কণাটির বিস্তার $A$, আদি দশা $\delta$, $t = 0$ সময়ে সরণ $x(0)$ এবং সর্বোচ্চ দ্রুতি $v_{\max}$ কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 2)।</t>
+          <t>আদর্শ সমীকরণ $x = A\sin(\omega t + \delta)$ এর সাথে তুলনা করে: বিস্তার $A = 0.08\text{ m} = 8\text{ cm}$। কৌণিক কম্পাঙ্ক $\omega = 10\pi\text{ rad/s}$। আদি দশা $\delta = \pi/4\text{ rad} = 45^\circ$। $t=0$-তে সরণ $x(0) = 0.08\sin(\pi/4) = \frac{0.08}{\sqrt{2}} \approx 0.0566\text{ m} = 5.66\text{ cm}$। সর্বোচ্চ দ্রুতি $v_{\max} = \omega A = 10\pi(0.08) = 0.8\pi \approx 2.513\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>$A = 0.08\text{ m}, \delta = 45^\circ, x(0) = 5.66\text{ cm}, v_{\max} = 2.51\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3640,43 +3421,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য (সমস্যা 3)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য]
-##PRESET:pendulum(15)[size:medium]##
-যে স্থানে $g = 9.8\text{ m/s}^2$, সেখানে একটি সঠিক সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য কত মিটার হতে হবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+সরল ছন্দিত গতিসম্পন্ন একটি কণার বিস্তার $A = 10\text{ cm}$ এবং পর্যায়কাল $T = 4.0\text{ s}$। সাম্যাবস্থান হতে সরণ $x = 6\text{ cm}$ অবস্থানে কণাটির বেগ এবং ত্বরণ কত?</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 3)।</t>
+          <t>কৌণিক কম্পাঙ্ক $\omega = \frac{2\pi}{T} = \frac{2\pi}{4} = \frac{\pi}{2} \approx 1.571\text{ rad/s}$। বেগ $v = \omega\sqrt{A^2 - x^2} = \frac{\pi}{2}\sqrt{10^2 - 6^2} = \frac{\pi}{2}\sqrt{64} = 4\pi \approx 12.57\text{ cm/s}$। ত্বরণ $a = -\omega^2 x = -\left(\frac{\pi}{2}\right)^2(6) = -1.5\pi^2 \approx -14.80\text{ cm/s}^2$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>বেগ $v = 12.57\text{ cm/s}$, ত্বরণ $a = -14.80\text{ cm/s}^2$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3696,7 +3472,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>দোলক ঘড়ির পাহাড়ে সময় হারানো (সমস্যা 4)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3709,25 +3485,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: দোলক ঘড়ির পাহাড়ে সময় হারানো]
-একটি সেকেন্ড দোলক ঘড়িকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে 10 সেকেন্ড সময় হারায়। পাহাড়টির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি কণা সরল ছন্দিত স্পন্দনে দোদুল্যমান। সাম্যাবস্থান হতে কোন অবস্থানে কণাটির বেগ তার সর্বোচ্চ বেগের অর্ধেক ($v = v_{\max}/2$) হবে?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 4)।</t>
+          <t>$v = \omega\sqrt{A^2 - x^2}$ এবং $v_{\max} = \omega A$। দেওয়া আছে $v = \frac{1}{2}v_{\max} \implies \omega\sqrt{A^2 - x^2} = \frac{1}{2}\omega A \implies \sqrt{A^2 - x^2} = \frac{A}{2}$। বর্গ করে: $A^2 - x^2 = \frac{A^2}{4} \implies x^2 = \frac{3}{4}A^2 \implies x = \pm \frac{\sqrt{3}}{2}A \approx \pm 0.866 A$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>$x = \frac{\sqrt{3}}{2}A \approx 0.866 A$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3747,38 +3523,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দনে শক্তি বিভাজন (সমস্যা 5)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: সরল ছন্দিত স্পন্দনে শক্তি বিভাজন]
-একটি সরল ছন্দিত স্পন্দকের মোট যান্ত্রিক শক্তি $E = 12\text{ J}$ এবং বিস্তার $A = 3\text{ cm}$। সাম্যাবস্থা হতে কত দূরত্বে কণাটির গতিশক্তি বিভবশক্তির সমান হবে?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+সরল ছন্দিত গতিসম্পন্ন একটি কণার সর্বোচ্চ বেগ $v_{\max} = 1.0\text{ m/s}$ এবং সর্বোচ্চ ত্বরণ $a_{\max} = 4.0\text{ m/s}^2$। কণাটির দোলনের বিস্তার $A$ এবং পর্যায়কাল $T$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 5)।</t>
+          <t>$v_{\max} = \omega A = 1.0$ এবং $a_{\max} = \omega^2 A = 4.0$। ভাগ করে: $\frac{a_{\max}}{v_{\max}} = \frac{\omega^2 A}{\omega A} = \omega \implies \omega = \frac{4.0}{1.0} = 4.0\text{ rad/s}$। বিস্তার $A = \frac{v_{\max}}{\omega} = \frac{1.0}{4.0} = 0.25\text{ m} = 25.0\text{ cm}$। পর্যায়কাল $T = \frac{2\pi}{\omega} = \frac{2\pi}{4.0} = \frac{\pi}{2} \approx 1.571\text{ s}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>$A = 0.25\text{ m} = 25.0\text{ cm}, T = 1.57\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3798,7 +3574,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>দোলকের ত্বরণ ও সর্বোচ্চ বেগ (সমস্যা 6)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3811,25 +3587,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: দোলকের ত্বরণ ও সর্বোচ্চ বেগ]
-একটি স্পন্দকের বিস্তার $A = 2\text{ cm}$ এবং পর্যায়কাল $T = 4\text{ s}$ হলে কণাটির সর্বোচ্চ দ্রুতি ($v_{max}$) এবং সর্বোচ্চ ত্বরণ ($a_{max}$) কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণার সরণ যখন $x_1 = 3\text{ cm}$, তখন এর বেগ $v_1 = 8\text{ cm/s}$; এবং যখন সরণ $x_2 = 4\text{ cm}$, তখন বেগ $v_2 = 6\text{ cm/s}$। কণাটির দোলনের বিস্তার এবং কম্পাঙ্ক নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 6)।</t>
+          <t>$v_1^2 = \omega^2(A^2 - x_1^2) \implies 64 = \omega^2(A^2 - 9)$ ... (১)। $v_2^2 = \omega^2(A^2 - x_2^2) \implies 36 = \omega^2(A^2 - 16)$ ... (২)। বিয়োগ করে: $64 - 36 = \omega^2(16 - 9) \implies 28 = 7\omega^2 \implies \omega^2 = 4 \implies \omega = 2.0\text{ rad/s}$। বিস্তার: $64 = 4(A^2 - 9) \implies A^2 - 9 = 16 \implies A^2 = 25 \implies A = 5.0\text{ cm}$। কম্পাঙ্ক $f = \frac{\omega}{2\pi} = \frac{2}{2\pi} = \frac{1}{\pi} \approx 0.318\text{ Hz}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t xml:space="preserve"> বিস্তার $A = 5.0\text{ cm}$, কম্পাঙ্ক $f = 0.318\text{ Hz}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3849,38 +3625,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>তরল স্তম্ভের দোলনকাল (U-টিউব) (সমস্যা 7)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: তরল স্তম্ভের দোলনকাল (U-টিউব)]
-একটি U-নলে $h = 4\text{ cm}$ উচ্চতার পারদ স্তম্ভ রাখা আছে। একপাশে সামান্য চাপ দিয়ে ছেড়ে দিলে পারদ স্তম্ভের সরল ছন্দিত দোলনের পর্যায়কাল $T = 2\pi \sqrt{\frac{h}{g}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি কণা সাম্যাবস্থান ($x = 0$) হতে সরল ছন্দিত স্পন্দন শুরু করে। কণাটির বিস্তার হতে অর্ধেক দূরত্বে ($x = A/2$) পৌঁছাতে সময় $t_1$ এবং পরবর্তী অর্ধাংশ ($x = A/2$ হতে $x = A$) পৌঁছাতে সময় $t_2$ লাগলে $t_1 : t_2$ অনুপাত নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 7)।</t>
+          <t>$x = A\sin(\omega t)$। $x = A/2$-এ: $\frac{A}{2} = A\sin(\omega t_1) \implies \sin(\omega t_1) = 1/2 \implies \omega t_1 = \frac{\pi}{6} \implies t_1 = \frac{T}{12}$। $x = A$-তে: $\omega(t_1 + t_2) = \frac{\pi}{2} \implies t_1 + t_2 = \frac{T}{4}$। $t_2 = \frac{T}{4} - \frac{T}{12} = \frac{2T}{12} = \frac{T}{6}$। অনুপাত $\frac{t_1}{t_2} = \frac{T/12}{T/6} = \frac{1}{2}$ বা $1 : 2$।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>$t_1 : t_2 = 1 : 2$</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3900,7 +3676,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর দোলন ও ভর পরিবর্তন (সমস্যা 8)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3913,25 +3689,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: স্প্রিং-এর দোলন ও ভর পরিবর্তন]
-একটি স্প্রিং-এ $m_1 = 6\text{ kg}$ ভর ঝুলালে পর্যায়কাল হয় $T_1 = 1.0\text{ s}$। এর সাথে অতিরিক্ত $m_2 = 6\text{ kg}$ ভর যুক্ত করলে নতুন পর্যায়কাল কত হবে?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##PRESET:vector-addition[size:medium]##
+একই সরলরেখা বরাবর একই কম্পাঙ্ক ও বিস্তারের দুটি সরল ছন্দিত তরঙ্গের উপরিপাতন হলো: $x_1 = A\sin(\omega t)$ এবং $x_2 = A\sin(\omega t + \phi)$। লব্ধি তরঙ্গের বিস্তার $A$ হওয়ার জন্য দশা পার্থক্য $\phi$ কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##PRESET:vector-addition[size:medium]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 8)।</t>
+          <t>লব্ধি বিস্তার $R = \sqrt{A^2 + A^2 + 2A^2\cos\phi} = \sqrt{2A^2(1+\cos\phi)} = 2A\cos(\phi/2)$। দেওয়া আছে $R = A \implies 2A\cos(\phi/2) = A \implies \cos(\phi/2) = 1/2 \implies \frac{\phi}{2} = 60^\circ \implies \phi = 120^\circ = \frac{2\pi}{3}\text{ rad}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>$\phi = 120^\circ = \frac{2\pi}{3}\text{ rad}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3951,38 +3727,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>দোলকের দোলন বিস্তার হ্রাস ও শক্তি (সমস্যা 9)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: দোলকের দোলন বিস্তার হ্রাস ও শক্তি]
-একটি অবমন্দিত সরল দোলকের বিস্তার প্রতি ১০টি দোলনে প্রাথমিক বিস্তারের $8\%$ হ্রাস পায়। এই সময়ে দোলকটির মোট শক্তি শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:circle[r=2.2][size:small]##
+একটি কণা $x = A\cos(\omega t)$ সমীকরণ অনুযায়ী স্পন্দিত হচ্ছে। $t = 0$ হতে যাত্রা শুরু করে কণাটি কোন সময়ে প্রথমবার তার সর্বোচ্চ দ্রুতি লাভ করবে?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.2][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 9)।</t>
+          <t>বেগ $v = \frac{dx}{dt} = -\omega A \sin(\omega t)$। সর্বোচ্চ দ্রুতি ঘটে যখন $|\sin(\omega t)| = 1 \implies \omega t = \frac{\pi}{2} \implies \left(\frac{2\pi}{T}\right)t = \frac{\pi}{2} \implies t = \frac{T}{4}$। কণাটি আদি অবস্থায় প্রান্তে ($x=A$) থাকে এবং $T/4$ সময়ে সাম্যাবস্থানে ($x=0$) পৌঁছানোর মুহূর্তে দ্রুতি সর্বোচ্চ হয়।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>$t = \frac{T}{4}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4002,7 +3778,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>কৌণিক সরল ছন্দিত গতি ও টর্ক (সমস্যা 10)</t>
+          <t>সরল ছন্দিত গতির ব্যবকলনীয় সমীকরণ ও গতিতত্ত্ব (SHM Differential Equation &amp; Kinematics)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4015,25 +3791,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: কৌণিক সরল ছন্দিত গতি ও টর্ক]
-একটি সুষম দণ্ডের একপ্রান্তে অনুভূমিক পেরেকের ওপর ঝুলিয়ে সামান্য দুলিয়ে দিলে এর দোলনকাল কত হবে? ($L = 10\text{ m}, g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি $m = 0.2\text{ kg}$ ভরের কণার সরল ছন্দিত গতির বিস্তার $A = 0.1\text{ m}$ এবং কম্পাঙ্ক $f = 5.0\text{ Hz}$। কণাটির সর্বোচ্চ পুনরুদ্ধার বল (Restoring force) কত নিউটন?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 10)।</t>
+          <t>কৌণিক কম্পাঙ্ক $\omega = 2\pi f = 2\pi(5) = 10\pi\text{ rad/s}$। সর্বোচ্চ ত্বরণ $a_{\max} = \omega^2 A = (10\pi)^2(0.1) = 100\pi^2(0.1) = 10\pi^2 \approx 98.70\text{ m/s}^2$। সর্বোচ্চ বল $F_{\max} = m a_{\max} = 0.2 \times 98.70 \approx 19.74\text{ N}$।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>$F_{\max} = 19.74\text{ N}$</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4053,38 +3829,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত গতির সরণ ও বেগ (সমস্যা 11)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>[সমস্যা 11: সরল ছন্দিত গতির সরণ ও বেগ]
-একটি কণা $x(t) = 12 \sin(4\pi t + \frac{\pi}{7})\text{ cm}$ সমীকরণানুযায়ী সরল ছন্দিত স্পন্দনে গতিশীল। কণাটির বিস্তার, পর্যায়কাল, এবং $t = 0.5\text{ s}$-এ বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+সরল ছন্দিত স্পন্দনরত একটি কণার বিস্তার $A$। সাম্যাবস্থান হতে সরণ কত হলে কণাটির গতিশক্তি ও বিভব শক্তি পরস্পর সমান ($K = U$) হবে? এবং কোন অবস্থানে গতিশক্তি বিভব শক্তির তিনগুণ ($K = 3U$) হবে?</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 11)।</t>
+          <t>গতিশক্তি $K = \frac{1}{2}m\omega^2(A^2 - x^2)$, বিভবশক্তি $U = \frac{1}{2}m\omega^2 x^2$। (১) $K = U \implies A^2 - x^2 = x^2 \implies 2x^2 = A^2 \implies x = \frac{A}{\sqrt{2}}$। (২) $K = 3U \implies A^2 - x^2 = 3x^2 \implies 4x^2 = A^2 \implies x = \frac{A}{2}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$K = U$ হয় $x = \frac{A}{\sqrt{2}} \approx 0.707A$-তে; $K = 3U$ হয় $x = \frac{A}{2}$-তে</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4104,7 +3880,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>স্প্রিং সমবায় ও তুল্য দোলনকাল (সমস্যা 12)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4117,30 +3893,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>[সমস্যা 12: স্প্রিং সমবায় ও তুল্য দোলনকাল]
-##PRESET:spring-mass[size:medium]##
-$k_1 = 200\text{ N/m}$ এবং $k_2 = 500\text{ N/m}$ স্প্রিং ধ্রুবকের দুটি স্প্রিংকে শ্রেণিতে এবং সমান্তরালে যুক্ত করে $M = 2\text{ kg}$ ভর ঝুলালে উভয় ক্ষেত্রে পর্যায়কাল কত হবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $0.5\text{ kg}$ ভরের কণা সরল ছন্দিত গতিতে স্পন্দিত হচ্ছে যার বিস্তার $A = 0.2\text{ m}$ এবং পর্যায়কাল $T = 2.0\text{ s}$। কণাটির মোট যান্ত্রিক শক্তি $E$ কত এবং সাম্যাবস্থান হতে $x = 0.1\text{ m}$ অবস্থানে কণার গতিশক্তি ও বিভবশক্তি নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 12)।</t>
+          <t>কৌণিক কম্পাঙ্ক $\omega = \frac{2\pi}{T} = \pi\text{ rad/s}$। মোট যান্ত্রিক শক্তি $E = \frac{1}{2}m\omega^2 A^2 = \frac{1}{2}(0.5)(\pi^2)(0.2^2) = 0.25(9.87)(0.04) = 0.01 \times 9.87 \approx 0.0987\text{ J}$। $x = 0.1\text{ m} = A/2$-এ: বিভবশক্তি $U = \frac{1}{4}E = \frac{0.0987}{4} \approx 0.0247\text{ J}$। গতিশক্তি $K = E - U = 0.0987 - 0.0247 = 0.0740\text{ J}$।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>$E = 0.0987\text{ J}, U = 0.0247\text{ J}, K = 0.0740\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4160,43 +3931,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য (সমস্যা 13)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য]
-##PRESET:pendulum(15)[size:medium]##
-যে স্থানে $g = 9.4\text{ m/s}^2$, সেখানে একটি সঠিক সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য কত মিটার হতে হবে?</t>
+          <t>##GEO:rect[w=3.5,h=2][size:small]##
+সরল ছন্দিত গতিতে স্পন্দনরত কোনো কণার বিভব শক্তির স্পন্দন কম্পাঙ্ক কণার মূল দোলন কম্পাঙ্কের কত গুণ তা গাণিতিকভাবে প্রমাণ কর।</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##GEO:rect[w=3.5,h=2][size:small]##</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 13)।</t>
+          <t>সরণ $x = A\sin(\omega t)$ হলে বিভবশক্তি $U(t) = \frac{1}{2}k x^2 = \frac{1}{2}k A^2 \sin^2(\omega t) = \frac{1}{4}k A^2 (1 - \cos 2\omega t)$। সমীকরণে কৌণিক কম্পাঙ্ক $2\omega$, যা মূল গতির দ্বিগুণ। সুতরাং বিভব শক্তি ও গতিশক্তি প্রতি পূর্ণ দোলনে দুবার সর্বোচ্চ মানে পৌঁছায়, অর্থাৎ তাদের কম্পাঙ্ক মূল কম্পাঙ্কের দ্বিগুণ।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>বিভব শক্তির কম্পাঙ্ক দ্বিগুণ ($f_U = 2f$)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4216,7 +3982,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>দোলক ঘড়ির পাহাড়ে সময় হারানো (সমস্যা 14)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4229,25 +3995,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: দোলক ঘড়ির পাহাড়ে সময় হারানো]
-একটি সেকেন্ড দোলক ঘড়িকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে 6 সেকেন্ড সময় হারায়। পাহাড়টির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি কণার মোট শক্তি $E = 16\text{ J}$ এবং বিস্তার $A = 4.0\text{ m}$। কণাটির বল ধ্রুবক $k$ নির্ণয় কর এবং কোন অবস্থানে কণাটির বিভবশক্তি মোট শক্তির $75\%$ হবে?</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 14)।</t>
+          <t>মোট শক্তি $E = \frac{1}{2}k A^2 \implies 16 = \frac{1}{2}k(16) = 8k \implies k = 2.0\text{ N/m}$। বিভবশক্তি $U = 0.75E \implies \frac{1}{2}k x^2 = \frac{3}{4}\left(\frac{1}{2}k A^2\right) \implies x^2 = \frac{3}{4}A^2 \implies x = \frac{\sqrt{3}}{2}A = \frac{\sqrt{3}}{2}(4) = 2\sqrt{3} \approx 3.46\text{ m}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>$k = 2.0\text{ N/m}, x = 2\sqrt{3}\text{ m} \approx 3.46\text{ m}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4267,38 +4033,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দনে শক্তি বিভাজন (সমস্যা 15)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: সরল ছন্দিত স্পন্দনে শক্তি বিভাজন]
-একটি সরল ছন্দিত স্পন্দকের মোট যান্ত্রিক শক্তি $E = 8\text{ J}$ এবং বিস্তার $A = 3\text{ cm}$। সাম্যাবস্থা হতে কত দূরত্বে কণাটির গতিশক্তি বিভবশক্তির সমান হবে?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি সরল ছন্দিত স্পন্দনশীল কণার গড় গতিশক্তি এবং গড় বিভবশক্তি একটি পূর্ণ চক্রের জন্য কত তা প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 15)।</t>
+          <t>এক পর্যায়কালে $\langle \sin^2(\omega t) \rangle = \frac{1}{2}$ এবং $\langle \cos^2(\omega t) \rangle = \frac{1}{2}$। গড় বিভবশক্তি $\langle U \rangle = \frac{1}{2}k A^2 \langle \sin^2(\omega t) \rangle = \frac{1}{4}kA^2 = \frac{E}{2}$। গড় গতিশক্তি $\langle K \rangle = \frac{1}{2}k A^2 \langle \cos^2(\omega t) \rangle = \frac{1}{4}kA^2 = \frac{E}{2}$। অর্থাৎ সময়ের সাপেক্ষে গড় গতিশক্তি ও গড় বিভবশক্তি পরস্পর সমান এবং মোট শক্তির অর্ধেক।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>$\langle K \rangle = \langle U \rangle = \frac{1}{4}m\omega^2 A^2 = \frac{E}{2}$</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4318,7 +4084,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>দোলকের ত্বরণ ও সর্বোচ্চ বেগ (সমস্যা 16)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4331,25 +4097,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: দোলকের ত্বরণ ও সর্বোচ্চ বেগ]
-একটি স্পন্দকের বিস্তার $A = 10\text{ cm}$ এবং পর্যায়কাল $T = 4\text{ s}$ হলে কণাটির সর্বোচ্চ দ্রুতি ($v_{max}$) এবং সর্বোচ্চ ত্বরণ ($a_{max}$) কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং-ভর ব্যবস্থার ভর $m = 1.0\text{ kg}$ এবং স্প্রিং ধ্রুবক $k = 100\text{ N/m}$। স্প্রিংটিকে $x_0 = 0.2\text{ m}$ সংকুচিত করে ছেড়ে দিলে সাম্যাবস্থান অতিক্রমকালে কণাটির গতিশক্তি কত হবে?</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 16)।</t>
+          <t>সাম্যাবস্থানে সমস্ত স্থিতিশক্তি গতিশক্তিতে রূপান্তর হয়: $K = E = \frac{1}{2}k x_0^2 = \frac{1}{2}(100)(0.2^2) = 50(0.04) = 2.0\text{ J}$।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>$K = 2.0\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4369,38 +4135,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>তরল স্তম্ভের দোলনকাল (U-টিউব) (সমস্যা 17)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: তরল স্তম্ভের দোলনকাল (U-টিউব)]
-একটি U-নলে $h = 12\text{ cm}$ উচ্চতার পারদ স্তম্ভ রাখা আছে। একপাশে সামান্য চাপ দিয়ে ছেড়ে দিলে পারদ স্তম্ভের সরল ছন্দিত দোলনের পর্যায়কাল $T = 2\pi \sqrt{\frac{h}{g}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2][size:small]##
+একটি কণা সরল ছন্দিত স্পন্দনে চলছে। বিস্তার $A = 5\text{ cm}$ হলে সাম্যাবস্থান হতে কত দূরত্বে কণাটির বিভবশক্তি তার গতিশক্তির এক-তৃতীয়াংশ ($U = K/3$) হবে?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 17)।</t>
+          <t>$U = \frac{1}{3}K \implies 3U = K \implies 3\left(\frac{1}{2}kx^2\right) = \frac{1}{2}k(A^2 - x^2) \implies 3x^2 = A^2 - x^2 \implies 4x^2 = A^2 \implies x = \frac{A}{2} = \frac{5}{2} = 2.5\text{ cm}$।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>$x = 2.5\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4420,7 +4186,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর দোলন ও ভর পরিবর্তন (সমস্যা 18)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4433,25 +4199,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: স্প্রিং-এর দোলন ও ভর পরিবর্তন]
-একটি স্প্রিং-এ $m_1 = 2\text{ kg}$ ভর ঝুলালে পর্যায়কাল হয় $T_1 = 1.0\text{ s}$। এর সাথে অতিরিক্ত $m_2 = 6\text{ kg}$ ভর যুক্ত করলে নতুন পর্যায়কাল কত হবে?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##
+একটি স্পন্দনশীল বস্তুর গতিশক্তি সময়ের সাথে $K(t) = K_0 \cos^2(100t)$ অনুসারে পরিবর্তিত হয়। গতির কম্পাঙ্ক এবং পর্যায়কাল কত?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=1.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 18)।</t>
+          <t>গতিশক্তির কৌণিক কম্পাঙ্ক $2\omega = 200 \implies \omega = 100\text{ rad/s}$। কম্পাঙ্ক $f = \frac{\omega}{2\pi} = \frac{100}{2\pi} \approx 15.92\text{ Hz}$। পর্যায়কাল $T = \frac{1}{f} = \frac{2\pi}{100} \approx 0.0628\text{ s}$।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>$f = 15.92\text{ Hz}, T = 0.0628\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4471,38 +4237,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>দোলকের দোলন বিস্তার হ্রাস ও শক্তি (সমস্যা 19)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: দোলকের দোলন বিস্তার হ্রাস ও শক্তি]
-একটি অবমন্দিত সরল দোলকের বিস্তার প্রতি ১০টি দোলনে প্রাথমিক বিস্তারের $4\%$ হ্রাস পায়। এই সময়ে দোলকটির মোট শক্তি শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=2][size:small]##
+একটি সরল ছন্দিত স্পন্দনে কণার ভর $m$। কণাটির সর্বোচ্চ ত্বরণ $\alpha$ এবং সর্বোচ্চ বেগ $\beta$ হলে এর মোট যান্ত্রিক শক্তি $E$-এর মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 19)।</t>
+          <t>সর্বোচ্চ বেগ $\beta = \omega A \implies \omega = \frac{\alpha}{\beta}$ কারণ $\alpha = \omega^2 A = \omega \beta \implies \omega = \frac{\alpha}{\beta}$। আবার $A = \frac{\beta}{\omega} = \frac{\beta^2}{\alpha}$। মোট শক্তি $E = \frac{1}{2}m \beta^2$ (সর্বোচ্চ গতিশক্তি হিসেবে)।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>$E = \frac{1}{2}m\beta^2 = \frac{m\beta^4}{2A^2}$ অথবা $E = \frac{m\beta^3}{2\alpha}$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4522,7 +4288,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>কৌণিক সরল ছন্দিত গতি ও টর্ক (সমস্যা 20)</t>
+          <t>সরল ছন্দিত গতির শক্তি ও শক্তি রূপান্তর (Energy of SHM &amp; Conservation)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4535,25 +4301,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: কৌণিক সরল ছন্দিত গতি ও টর্ক]
-একটি সুষম দণ্ডের একপ্রান্তে অনুভূমিক পেরেকের ওপর ঝুলিয়ে সামান্য দুলিয়ে দিলে এর দোলনকাল কত হবে? ($L = 6\text{ m}, g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি কণার গতিশক্তি ও স্থিতিশক্তির লেখচিত্রের ছেদবিন্দুগুলোতে সরণের মান কত এবং মোট শক্তির সাথে তুলনা কর।</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 20)।</t>
+          <t>ছেদবিন্দুতে $K = U \implies \frac{1}{2}k(A^2 - x^2) = \frac{1}{2}kx^2 \implies x = \pm \frac{A}{\sqrt{2}}$। ওই বিন্দুতে বিভবশক্তি ও গতিশক্তি উভয়ের মানই মোট শক্তির অর্ধেক: $K = U = \frac{E}{2}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>$x = \pm \frac{A}{\sqrt{2}}$, প্রতিটি শক্তি $E/2$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4573,38 +4339,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত গতির সরণ ও বেগ (সমস্যা 21)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>[সমস্যা 21: সরল ছন্দিত গতির সরণ ও বেগ]
-একটি কণা $x(t) = 8 \sin(4\pi t + \frac{\pi}{5})\text{ cm}$ সমীকরণানুযায়ী সরল ছন্দিত স্পন্দনে গতিশীল। কণাটির বিস্তার, পর্যায়কাল, এবং $t = 0.5\text{ s}$-এ বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+একটি সেকেন্ড দোলকের পর্যায়কাল $T = 2.0\text{ s}$। দোলকটিকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে $30\text{ সেকেন্ড}$ ধীরে চলে। পাহাড়ের উচ্চতা কত? (পৃথিবীর ব্যাসার্ধ $R = 6400\text{ km}$)।</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 21)।</t>
+          <t>পাহাড়ের চূড়ায় প্রতিদিনের হারানো সময় $\Delta T = 86400\frac{h}{R} \implies 30 = 86400 \frac{h}{6400} \implies h = \frac{30 \times 6400}{86400} = \frac{192000}{86400} \approx 2.222\text{ km}$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>পাহাড়ের উচ্চতা $h = 2.22\text{ km}$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4624,7 +4390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>স্প্রিং সমবায় ও তুল্য দোলনকাল (সমস্যা 22)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4637,30 +4403,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>[সমস্যা 22: স্প্রিং সমবায় ও তুল্য দোলনকাল]
-##PRESET:spring-mass[size:medium]##
-$k_1 = 1000\text{ N/m}$ এবং $k_2 = 500\text{ N/m}$ স্প্রিং ধ্রুবকের দুটি স্প্রিংকে শ্রেণিতে এবং সমান্তরালে যুক্ত করে $M = 2\text{ kg}$ ভর ঝুলালে উভয় ক্ষেত্রে পর্যায়কাল কত হবে?</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+একটি সরল দোলকের ববকে একটি তরলে নিমজ্জিত করে দোলানো হলো যার ঘনত্ব ববের ঘনত্বের $1/4$ অংশ (সান্দ্রতা অগ্রাহ্য করে)। তরলে দোলকটির পর্যায়কাল বায়ুর পর্যায়কালের কত গুণ হবে?</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 22)।</t>
+          <t>ববের আপাত ওজন $W' = V\rho g - V\sigma g = V\rho g(1 - \sigma/\rho) = mg(1 - 1/4) = \frac{3}{4}mg$। কার্যকর ত্বরণ $g' = \frac{3}{4}g$। নতুন পর্যায়কাল $T' = 2\pi\sqrt{\frac{L}{g'}} = 2\pi\sqrt{\frac{L}{\frac{3}{4}g}} = \frac{2}{\sqrt{3}}\left(2\pi\sqrt{\frac{L}{g}}\right) = \frac{2}{\sqrt{3}}T \approx 1.155 T$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$T' = \frac{2}{\sqrt{3}}T \approx 1.155 T$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4680,43 +4441,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য (সমস্যা 23)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য]
-##PRESET:pendulum(15)[size:medium]##
-যে স্থানে $g = 9.12\text{ m/s}^2$, সেখানে একটি সঠিক সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য কত মিটার হতে হবে?</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+একটি লিফট $a = 2.0\text{ m/s}^2$ ত্বরণে (ক) খাড়া উপরে উঠলে এবং (খ) খাড়া নিচে নামলে একটি সেকেন্ড দোলকের নতুন পর্যায়কাল কত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 23)।</t>
+          <t>সেকেন্ড দোলকের দৈর্ঘ্য $L = \frac{g T^2}{4\pi^2} = \frac{9.8(4)}{4\pi^2} \approx 0.993\text{ m}$। (ক) উপরে উঠলে কার্যকর ত্বরণ $g_{eff} = g + a = 9.8 + 2.0 = 11.8\text{ m/s}^2$। $T_1 = 2\pi\sqrt{\frac{0.993}{11.8}} = 2\pi\sqrt{0.08415} \approx 1.823\text{ s}$। (খ) নিচে নামলে $g_{eff} = g - a = 9.8 - 2.0 = 7.8\text{ m/s}^2$। $T_2 = 2\pi\sqrt{\frac{0.993}{7.8}} = 2\pi\sqrt{0.1273} \approx 2.242\text{ s}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>(ক) উপরে উঠলে $T_1 = 1.82\text{ s}$, (খ) নিচে নামলে $T_2 = 2.24\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4736,7 +4492,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>দোলক ঘড়ির পাহাড়ে সময় হারানো (সমস্যা 24)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4749,25 +4505,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: দোলক ঘড়ির পাহাড়ে সময় হারানো]
-একটি সেকেন্ড দোলক ঘড়িকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে 2 সেকেন্ড সময় হারায়। পাহাড়টির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=12,length=4][size:small]##
+একটি সেকেন্ড দোলকের তাপমাত্রা $20^\circ\text{C}$ বৃদ্ধি পেলে ঘড়িটি প্রতিদিন কত সেকেন্ড ধীরে চলবে? (দণ্ডটির রৈখিক প্রসারণ সহগ $\alpha = 1.2 	imes 10^{-5}\text{ K}^{-1}$)।</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=12,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 24)।</t>
+          <t>তাপমাত্রা বৃদ্ধির জন্য পর্যায়কালের পরিবর্তন $\frac{\Delta T}{T} = \frac{1}{2}\alpha\Delta\theta$। প্রতিদিন হারানো সময় $\Delta t = 86400 \times \frac{1}{2}\alpha\Delta\theta = 43200 \times (1.2\times 10^{-5}) \times 20 = 43200 \times (2.4\times 10^{-4}) = 10.368\text{ s} \approx 10.37\text{ s}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>প্রতিদিন হারানো সময় $\Delta T = 10.37\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4787,38 +4543,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দনে শক্তি বিভাজন (সমস্যা 25)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: সরল ছন্দিত স্পন্দনে শক্তি বিভাজন]
-একটি সরল ছন্দিত স্পন্দকের মোট যান্ত্রিক শক্তি $E = 4\text{ J}$ এবং বিস্তার $A = 3\text{ cm}$। সাম্যাবস্থা হতে কত দূরত্বে কণাটির গতিশক্তি বিভবশক্তির সমান হবে?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=4.5][size:small]##
+একটি সরল দোলকের কার্যকর দৈর্ঘ্য $21\%$ বৃদ্ধি করা হলে এর পর্যায়কাল শতকরা কত বৃদ্ধি পাবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=4.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 25)।</t>
+          <t>$T = 2\pi\sqrt{\frac{L}{g}} \propto \sqrt{L}$। নতুন দৈর্ঘ্য $L' = 1.21 L$। নতুন পর্যায়কাল $T' = \sqrt{1.21} T = 1.10 T$। পর্যায়কালের শতকরা বৃদ্ধি $= (1.10 - 1) \times 100\% = 10.0\%$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>পর্যায়কাল বৃদ্ধি পাবে $10.0\%$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4838,7 +4594,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>দোলকের ত্বরণ ও সর্বোচ্চ বেগ (সমস্যা 26)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -4851,25 +4607,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: দোলকের ত্বরণ ও সর্বোচ্চ বেগ]
-একটি স্পন্দকের বিস্তার $A = 6\text{ cm}$ এবং পর্যায়কাল $T = 4\text{ s}$ হলে কণাটির সর্বোচ্চ দ্রুতি ($v_{max}$) এবং সর্বোচ্চ ত্বরণ ($a_{max}$) কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=14,length=4][size:small]##
+একটি গাড়ি $a = 2.5\text{ m/s}^2$ সমত্বরণে অনুভূমিক রাস্তায় চলছে। গাড়ির ছাদ হতে ঝুলানো একটি সরল দোলকের কার্যকর পর্যায়কাল কত হবে যদি স্থির অবস্থায় এর পর্যায়কাল $2.0\text{ s}$ হয়? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=14,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 26)।</t>
+          <t>ত্বরান্বিত গাড়িতে কার্যকর অভিকর্ষজ ত্বরণ $g_{eff} = \sqrt{g^2 + a^2} = \sqrt{9.8^2 + 2.5^2} = \sqrt{96.04 + 6.25} = \sqrt{102.29} \approx 10.114\text{ m/s}^2$। পর্যায়কাল $T' = T\sqrt{\frac{g}{g_{eff}}} = 2.0\sqrt{\frac{9.8}{10.114}} = 2.0\sqrt{0.9689} \approx 1.969\text{ s} \approx 1.97\text{ s}$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>পর্যায়কাল $T' = 1.97\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4889,38 +4645,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>তরল স্তম্ভের দোলনকাল (U-টিউব) (সমস্যা 27)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: তরল স্তম্ভের দোলনকাল (U-টিউব)]
-একটি U-নলে $h = 8\text{ cm}$ উচ্চতার পারদ স্তম্ভ রাখা আছে। একপাশে সামান্য চাপ দিয়ে ছেড়ে দিলে পারদ স্তম্ভের সরল ছন্দিত দোলনের পর্যায়কাল $T = 2\pi \sqrt{\frac{h}{g}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=2.5][size:small]##
+চাঁদের পৃষ্ঠে অভিকর্ষজ ত্বরণ পৃথিবীর ত্বরণের $1/6$ অংশ। পৃথিবীতে একটি সেকেন্ড দোলকের দৈর্ঘ্য $L_E = 1.0\text{ m}$ হলে চাঁদের পৃষ্ঠে একটি সেকেন্ড দোলকের দৈর্ঘ্য কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 27)।</t>
+          <t>সেকেন্ড দোলকের পর্যায়কাল $T = 2\text{ s}$ ধ্রুব: $T = 2\pi\sqrt{\frac{L}{g}} \implies L \propto g$। চাঁদে দৈর্ঘ্য $L_M = L_E \left(\frac{g_M}{g_E}\right) = 1.0 \times \frac{1}{6} \approx 0.1667\text{ m} = 16.67\text{ cm}$।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>$L_M = \frac{1}{6}\text{ m} \approx 0.167\text{ m} = 16.67\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4940,7 +4696,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর দোলন ও ভর পরিবর্তন (সমস্যা 28)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -4953,25 +4709,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: স্প্রিং-এর দোলন ও ভর পরিবর্তন]
-একটি স্প্রিং-এ $m_1 = 10\text{ kg}$ ভর ঝুলালে পর্যায়কাল হয় $T_1 = 1.0\text{ s}$। এর সাথে অতিরিক্ত $m_2 = 6\text{ kg}$ ভর যুক্ত করলে নতুন পর্যায়কাল কত হবে?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সরল দোলক পৃথিবীর কেন্দ্র দিয়ে নির্মিত সুরঙ্গের মধ্যে নিয়ে গেলে এর দোলনকাল কত হবে? (ব্যাখ্যা কর কেন কেন্দ্রস্থলে দোলক অচল হয়ে যায়)।</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 28)।</t>
+          <t>পৃথিবীর কেন্দ্রে অভিকর্ষজ ত্বরণ $g = 0$। পর্যায়কালের সূত্র $T = 2\pi\sqrt{\frac{L}{g}}$ অনুসারে $g \to 0$ হলে $T \to \infty$। কেন্দ্রে কোনো পুনরুদ্ধার অভিকর্ষজ বল না থাকায় দোলকের কোনো প্রত্যাবর্তনমূলক স্পন্দন সম্ভব নয় এবং দোলকটি অচল হয়ে যাবে।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>কেন্দ্রে পর্যায়কাল অসীম ($T = \infty$), দোলক অচল হবে</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4991,38 +4747,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>দোলকের দোলন বিস্তার হ্রাস ও শক্তি (সমস্যা 29)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: দোলকের দোলন বিস্তার হ্রাস ও শক্তি]
-একটি অবমন্দিত সরল দোলকের বিস্তার প্রতি ১০টি দোলনে প্রাথমিক বিস্তারের $12\%$ হ্রাস পায়। এই সময়ে দোলকটির মোট শক্তি শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##
+একটি পেন্ডুলাম ঘড়ি শীতকালে প্রতিদিন $15\text{ সেকেন্ড}$ দ্রুত চলে এবং গ্রীষ্মকালে প্রতিদিন $25\text{ সেকেন্ড}$ ধীরে চলে। উভয় ঋতুর তাপমাত্রার পার্থক্য কত? (দণ্ডের $\alpha = 2.0 	imes 10^{-5}\text{ K}^{-1}$)।</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=15,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 29)।</t>
+          <t>শীত ও গ্রীষ্মে মোট সময়ের ব্যবধান $\Delta t = 15 - (-25) = 40\text{ s}$। $\Delta t = 86400 \times \frac{1}{2}\alpha\Delta\theta \implies 40 = 43200 \times (2.0\times 10^{-5})\Delta\theta = 0.864\Delta\theta \implies \Delta\theta = \frac{40}{0.864} \approx 46.30^\circ\text{C}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>তাপমাত্রার পার্থক্য $\Delta\theta = 46.3^\circ\text{C}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5042,7 +4798,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>কৌণিক সরল ছন্দিত গতি ও টর্ক (সমস্যা 30)</t>
+          <t>সরল দোলক, তাপমাত্রা ও অভিকর্ষের প্রভাব (Simple Pendulum &amp; Clocks)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5055,25 +4811,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: কৌণিক সরল ছন্দিত গতি ও টর্ক]
-একটি সুষম দণ্ডের একপ্রান্তে অনুভূমিক পেরেকের ওপর ঝুলিয়ে সামান্য দুলিয়ে দিলে এর দোলনকাল কত হবে? ($L = 2\text{ m}, g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:pendulum[angle=60,length=4][size:small]##
+একটি সরল দোলকের কৌণিক বিস্তার $\theta_0 = 60^\circ$ হলে এর ক্ষুদ্র বিস্তার অনুমানের সাথে প্রকৃত দোলনকালের পার্থক্য কত শতাংশ? (বৃহৎ বিস্তারে $T pprox T_0(1 + \frac{1}{16}\theta_0^2)$)।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:pendulum[angle=60,length=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 30)।</t>
+          <t>কৌণিক বিস্তার রেডিয়ানে: $\theta_0 = 60^\circ = \frac{\pi}{3} \approx 1.0472\text{ rad}$। দ্বিতীয় ক্রমের সংশোধন: $\frac{\Delta T}{T_0} \approx \frac{1}{16}\theta_0^2 = \frac{1}{16}(1.0472)^2 = \frac{1.0966}{16} \approx 0.0685 = 6.85\%$।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>দোলনকাল বৃদ্ধি পায় প্রায় $6.85\%$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5093,38 +4849,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত গতির সরণ ও বেগ (সমস্যা 31)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>[সমস্যা 31: সরল ছন্দিত গতির সরণ ও বেগ]
-একটি কণা $x(t) = 4 \sin(4\pi t + \frac{\pi}{7})\text{ cm}$ সমীকরণানুযায়ী সরল ছন্দিত স্পন্দনে গতিশীল। কণাটির বিস্তার, পর্যায়কাল, এবং $t = 0.5\text{ s}$-এ বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+দুটি স্প্রিং-এর স্প্রিং ধ্রুবক যথাক্রমে $k_1 = 300\text{ N/m}$ এবং $k_2 = 600\text{ N/m}$। স্প্রিং দুটিকে (ক) শ্রেণি সমবায়ে এবং (খ) সমান্তরাল সমবায়ে যুক্ত করে $m = 2.0\text{ kg}$ ভরের বস্তু ঝুলালে উভয় ক্ষেত্রে দোলনকাল কত হবে?</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 31)।</t>
+          <t>(ক) শ্রেণি সমবায়ে: $k_s = \frac{k_1 k_2}{k_1 + k_2} = \frac{300 \times 600}{900} = 200\text{ N/m}$। $T_s = 2\pi\sqrt{\frac{m}{k_s}} = 2\pi\sqrt{\frac{2.0}{200}} = 2\pi\sqrt{0.01} = 0.2\pi \approx 0.628\text{ s}$। (খ) সমান্তরালে: $k_p = k_1 + k_2 = 300 + 600 = 900\text{ N/m}$। $T_p = 2\pi\sqrt{\frac{m}{k_p}} = 2\pi\sqrt{\frac{2.0}{900}} = \frac{2\pi\sqrt{2}}{30} \approx 0.296\text{ s}$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>(ক) শ্রেণিতে $T_s = 0.628\text{ s}$, (খ) সমান্তরালে $T_p = 0.296\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5144,12 +4900,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>স্প্রিং সমবায় ও তুল্য দোলনকাল (সমস্যা 32)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5157,30 +4913,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>[সমস্যা 32: স্প্রিং সমবায় ও তুল্য দোলনকাল]
-##PRESET:spring-mass[size:medium]##
-$k_1 = 600\text{ N/m}$ এবং $k_2 = 500\text{ N/m}$ স্প্রিং ধ্রুবকের দুটি স্প্রিংকে শ্রেণিতে এবং সমান্তরালে যুক্ত করে $M = 2\text{ kg}$ ভর ঝুলালে উভয় ক্ষেত্রে পর্যায়কাল কত হবে?</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং-এর সাথে $M$ ভর ঝুলালে এর পর্যায়কাল হয় $2.0\text{ s}$। ভর $2\text{ kg}$ বৃদ্ধি করলে পর্যায়কাল বেড়ে $3.0\text{ s}$ হয়। আদি ভর $M$ এবং স্প্রিং ধ্রুবক $k$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 32)।</t>
+          <t>$T_1 = 2\pi\sqrt{\frac{M}{k}} = 2.0$ এবং $T_2 = 2\pi\sqrt{\frac{M+2}{k}} = 3.0$। ভাগ করে: $\frac{T_2}{T_1} = \sqrt{\frac{M+2}{M}} = \frac{3}{2}$। বর্গ করে: $\frac{M+2}{M} = \frac{9}{4} \implies 4M + 8 = 9M \implies 5M = 8 \implies M = 1.60\text{ kg}$। স্প্রিং ধ্রুবক $k = \frac{4\pi^2 M}{T_1^2} = \frac{4\pi^2(1.6)}{4} = 1.6\pi^2 \approx 15.79\text{ N/m}$।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>$M = 1.60\text{ kg}, k = 15.79\text{ N/m}$</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5200,43 +4951,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য (সমস্যা 33)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য]
-##PRESET:pendulum(15)[size:medium]##
-যে স্থানে $g = 9.8\text{ m/s}^2$, সেখানে একটি সঠিক সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য কত মিটার হতে হবে?</t>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং ধ্রুবক $k$-এর একটি স্প্রিংকে কেটে $1:2$ অনুপাতে দুটি টুকরা করা হলো। প্রতিটি টুকরার স্প্রিং ধ্রুবক কত হবে এবং ক্ষুদ্রতর টুকরায় $m$ ভর ঝুলালে দোলনকাল কত?</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 33)।</t>
+          <t>স্প্রিং ধ্রুবক দৈর্ঘ্যের ব্যস্তানুপাতিক ($k \propto 1/L$)। সম্পূর্ণ দৈর্ঘ্য $L$ হলে টুকরাদ্বয়ের দৈর্ঘ্য $L_1 = L/3$ এবং $L_2 = 2L/3$। ১ম টুকরার ধ্রুবক $k_1 = 3k$। ২য় টুকরার ধ্রুবক $k_2 = \frac{3}{2}k = 1.5k$। ১ম টুকরায় পর্যায়কাল $T = 2\pi\sqrt{\frac{m}{k_1}} = 2\pi\sqrt{\frac{m}{3k}}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>$k_1 = 3k, k_2 = 1.5k, T = 2\pi\sqrt{\frac{m}{3k}}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5256,12 +5002,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>দোলক ঘড়ির পাহাড়ে সময় হারানো (সমস্যা 34)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5269,25 +5015,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: দোলক ঘড়ির পাহাড়ে সময় হারানো]
-একটি সেকেন্ড দোলক ঘড়িকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে 10 সেকেন্ড সময় হারায়। পাহাড়টির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি সুষম $U$-নলে তরলের মোট দৈর্ঘ্য $L = 50\text{ cm}$। নলের একপ্রান্তে চাপ দিয়ে তরল স্তম্ভকে সামান্য আন্দোলিত করে ছেড়ে দিলে তরলের মুক্ত দোলনের পর্যায়কাল কত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 34)।</t>
+          <t>$U$-নলের তরল স্তম্ভের দোলনকাল $T = 2\pi\sqrt{\frac{L}{2g}}$ (যেখানে $L$ হলো নলের তরল স্তম্ভের মোট দৈর্ঘ্য)। মান বসিয়ে: $T = 2\pi\sqrt{\frac{0.50}{2(9.8)}} = 2\pi\sqrt{\frac{0.50}{19.6}} = 2\pi\sqrt{\frac{1}{39.2}} = \frac{2\pi}{6.261} \approx 1.003\text{ s} \approx 1.00\text{ s}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>পর্যায়কাল $T = 1.00\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5307,38 +5053,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দনে শক্তি বিভাজন (সমস্যা 35)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: সরল ছন্দিত স্পন্দনে শক্তি বিভাজন]
-একটি সরল ছন্দিত স্পন্দকের মোট যান্ত্রিক শক্তি $E = 12\text{ J}$ এবং বিস্তার $A = 3\text{ cm}$। সাম্যাবস্থা হতে কত দূরত্বে কণাটির গতিশক্তি বিভবশক্তির সমান হবে?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি $M = 500\text{ g}$ ভরের কাঠের ব্লক একটি উলম্ব স্প্রিং-এর ওপর ভারসাম্য অবস্থায় রাখা আছে। স্প্রিংটির ওপর কত সর্বোচ্চ বিস্তার পর্যন্ত স্পন্দন দিলে ব্লকটি স্প্রিং হতে বিচ্ছিন্ন হবে না? ($k = 200\text{ N/m}, g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 35)।</t>
+          <t>স্প্রিং হতে বিচ্ছিন্ন না হওয়ার শর্ত হলো শীর্ষবিন্দুতে নিম্নমুখী ত্বরণ $g$-এর চেয়ে বেশি হতে পারবে না: $a_{\max} \le g \implies \omega^2 A \le g$। $\omega^2 = \frac{k}{M} = \frac{200}{0.5} = 400\text{ s}^{-2}$। $400 A \le 9.8 \implies A_{\max} = \frac{9.8}{400} = 0.0245\text{ m} = 2.45\text{ cm}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>সর্বোচ্চ বিস্তার $A_{\max} = 2.45\text{ cm}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5358,12 +5104,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>দোলকের ত্বরণ ও সর্বোচ্চ বেগ (সমস্যা 36)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5371,25 +5117,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: দোলকের ত্বরণ ও সর্বোচ্চ বেগ]
-একটি স্পন্দকের বিস্তার $A = 2\text{ cm}$ এবং পর্যায়কাল $T = 4\text{ s}$ হলে কণাটির সর্বোচ্চ দ্রুতি ($v_{max}$) এবং সর্বোচ্চ ত্বরণ ($a_{max}$) কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি $m = 200\text{ g}$ ভরের সিলিন্ডার তরলে উল্লম্বভাবে ভাসছে। তরলের ঘনত্ব $\rho = 1000\text{ kg/m}^3$ এবং সিলিন্ডারের প্রস্থচ্ছেদ $A = 20\text{ cm}^2$। সিলিন্ডারটিকে সামান্য নিচে চেপে ছেড়ে দিলে এর দোলনকাল কত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 36)।</t>
+          <t>প্লবতা জনিত পুনরুদ্ধার বল $F = -A\rho g x$। কার্যকর স্প্রিং ধ্রুবক $k = A\rho g = (20\times 10^{-4}\text{ m}^2)(1000)(9.8) = 19.6\text{ N/m}$। পর্যায়কাল $T = 2\pi\sqrt{\frac{m}{k}} = 2\pi\sqrt{\frac{0.20}{19.6}} = 2\pi\sqrt{\frac{1}{98}} \approx \frac{2\pi}{9.899} \approx 0.6347\text{ s} \approx 0.635\text{ s}$।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$T = 0.635\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5409,38 +5155,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>তরল স্তম্ভের দোলনকাল (U-টিউব) (সমস্যা 37)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: তরল স্তম্ভের দোলনকাল (U-টিউব)]
-একটি U-নলে $h = 4\text{ cm}$ উচ্চতার পারদ স্তম্ভ রাখা আছে। একপাশে সামান্য চাপ দিয়ে ছেড়ে দিলে পারদ স্তম্ভের সরল ছন্দিত দোলনের পর্যায়কাল $T = 2\pi \sqrt{\frac{h}{g}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং ধ্রুবক $k$-এর উভয় প্রান্তে $m_1$ এবং $m_2$ ভরের দুটি বস্তু সংযুক্ত করে একটি মসৃণ অনুভূমিক মেঝের ওপর স্পন্দনশীল করা হলো। ব্যবস্থাটির কার্যকর হ্রাসকৃত ভর (Reduced mass) এবং দোলনকালের সমীকরণ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 37)।</t>
+          <t>ভরকেন্দ্র স্থির থাকায় উভয় ভরের স্পন্দন কম্পাঙ্ক অভিন্ন। সমতুল্য হ্রাসকৃত ভর $\mu = \frac{m_1 m_2}{m_1 + m_2}$। সমীকরণের পর্যায়কাল $T = 2\pi\sqrt{\frac{\mu}{k}} = 2\pi\sqrt{\frac{m_1 m_2}{(m_1+m_2)k}}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>$\mu = \frac{m_1 m_2}{m_1 + m_2}, T = 2\pi\sqrt{\frac{\mu}{k}}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5460,12 +5206,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর দোলন ও ভর পরিবর্তন (সমস্যা 38)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5473,25 +5219,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: স্প্রিং-এর দোলন ও ভর পরিবর্তন]
-একটি স্প্রিং-এ $m_1 = 6\text{ kg}$ ভর ঝুলালে পর্যায়কাল হয় $T_1 = 1.0\text{ s}$। এর সাথে অতিরিক্ত $m_2 = 6\text{ kg}$ ভর যুক্ত করলে নতুন পর্যায়কাল কত হবে?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি অবমন্দিত স্পন্দনের (Damped Oscillation) বিস্তার $10\text{ সেকেন্ডে}$ তার প্রারম্ভিক মানের অর্ধেকে নেমে আসে। প্রারম্ভিক মানের $1/8$ অংশে নামতে মোট কত সেকেন্ড সময় লাগবে?</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 38)।</t>
+          <t>অবমন্দিত বিস্তার $A(t) = A_0 e^{-\gamma t}$। বিস্তার অর্ধেক হতে সময় $t_{1/2} = 10\text{ s}$। বিস্তার $1/8 = (1/2)^3$ হতে তিনটি অর্ধায়ু সময় পার হতে হবে: $t = 3 \times t_{1/2} = 3 \times 10 = 30.0\text{ s}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>সময় $t = 30.0\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5511,38 +5257,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>দোলকের দোলন বিস্তার হ্রাস ও শক্তি (সমস্যা 39)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: দোলকের দোলন বিস্তার হ্রাস ও শক্তি]
-একটি অবমন্দিত সরল দোলকের বিস্তার প্রতি ১০টি দোলনে প্রাথমিক বিস্তারের $8\%$ হ্রাস পায়। এই সময়ে দোলকটির মোট শক্তি শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:rect[w=1,h=5][size:small]##
+একটি $L = 1.0\text{ m}$ দৈর্ঘ্যের সুষম সরু রডের একপ্রান্ত হতে লম্ব অক্ষের সাপেক্ষে দোদুল্যমান (Physical Pendulum)। রডটির ক্ষুদ্র দোলনের পর্যায়কাল কত? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=1,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 39)।</t>
+          <t>একপ্রান্ত সাপেক্ষে জড়তার ভ্রামক $I = \frac{1}{3}ML^2$। ভরকেন্দ্রের দূরত্ব $d = L/2$। চক্রগতির সূত্র: $T = 2\pi\sqrt{\frac{I}{mgd}} = 2\pi\sqrt{\frac{\frac{1}{3}ML^2}{Mg(L/2)}} = 2\pi\sqrt{\frac{2L}{3g}} = 2\pi\sqrt{\frac{2(1.0)}{3(9.8)}} = 2\pi\sqrt{\frac{2}{29.4}} = 2\pi\sqrt{0.0680} \approx 1.639\text{ s}$।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>পর্যায়কাল $T = 1.64\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5562,12 +5308,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>কৌণিক সরল ছন্দিত গতি ও টর্ক (সমস্যা 40)</t>
+          <t>স্প্রিং সমবায়, U-নল ও অবমন্দিত স্পন্দন (Springs, U-Tube &amp; Damped SHM)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5575,25 +5321,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: কৌণিক সরল ছন্দিত গতি ও টর্ক]
-একটি সুষম দণ্ডের একপ্রান্তে অনুভূমিক পেরেকের ওপর ঝুলিয়ে সামান্য দুলিয়ে দিলে এর দোলনকাল কত হবে? ($L = 10\text{ m}, g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি চালিত স্পন্দকে (Driven Oscillator) অনুনাদ সৃষ্টি হলে দোলকের বিস্তার সর্বোচ্চ হয়। অনুনাদের তীক্ষ্ণতা (Quality factor $Q$) বলতে কী বোঝায় এবং উচ্চ $Q$-এর অর্থ কী?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 40)।</t>
+          <t>গুণগত গুণক বা কোয়ালিটি ফ্যাক্টর $Q = 2\pi \frac{\text{সঞ্চিত শক্তি}}{\text{প্রতি চক্রে ক্ষয়িত শক্তি}} = \frac{\omega_0}{\Delta\omega}$ (যেখানে $\Delta\omega$ হলো ব্যান্ডউইডথ)। উচ্চ $Q$-মানের অর্থ হলো সিস্টেমে অবমন্দন খুব কম, অনুনাদ অত্যন্ত তীক্ষ্ণ এবং সামান্য কম্পাঙ্ক পরিবর্তনে বিস্তার তীব্রভাবে হ্রাস পায়।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>$Q = \frac{\omega_0}{2\gamma} = \frac{\omega_0}{\Delta\omega}$, উচ্চ $Q$ মানে অতি তীক্ষ্ণ অনুনাদ ও স্বল্প শক্তি অপচয়</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5613,38 +5359,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত গতির সরণ ও বেগ (সমস্যা 41)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>[সমস্যা 41: সরল ছন্দিত গতির সরণ ও বেগ]
-একটি কণা $x(t) = 12 \sin(4\pi t + \frac{\pi}{5})\text{ cm}$ সমীকরণানুযায়ী সরল ছন্দিত স্পন্দনে গতিশীল। কণাটির বিস্তার, পর্যায়কাল, এবং $t = 0.5\text{ s}$-এ বেগ কত?</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>##PRESET:simple-pendulum[size:small]##
+একটি লিফট $a = 2.45\text{ ms}^{-2}$ ত্বরণে উপরের দিকে উঠছে। লিফটের ভেতর একটি সেকেন্ড দোলকের কার্যকর দোলনকাল কত হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>##PRESET:simple-pendulum[size:small]##</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 41)।</t>
+          <t>স্থির লিফটে সেকেন্ড দোলকের দোলনকাল $T = 2\\text{ s}$। লিফট $a$ ত্বরণে উপরে উঠলে কার্যকর অভিকর্ষজ ত্বরণ $g' = g + a = 9.8 + 2.45 = 12.25\\text{ ms}^{-2}$। নতুন দোলনকাল $T' = T\\sqrt{\\frac{g}{g'}} = 2\\sqrt{\\frac{9.8}{12.25}} = 2\\sqrt{0.8} \\approx 2 \\times 0.8944 = 1.789\\text{ s} \\approx 1.79\\text{ s}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>কার্যকর দোলনকাল $T' = 1.79\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5664,12 +5410,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>স্প্রিং সমবায় ও তুল্য দোলনকাল (সমস্যা 42)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5677,30 +5423,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>[সমস্যা 42: স্প্রিং সমবায় ও তুল্য দোলনকাল]
-##PRESET:spring-mass[size:medium]##
-$k_1 = 200\text{ N/m}$ এবং $k_2 = 500\text{ N/m}$ স্প্রিং ধ্রুবকের দুটি স্প্রিংকে শ্রেণিতে এবং সমান্তরালে যুক্ত করে $M = 2\text{ kg}$ ভর ঝুলালে উভয় ক্ষেত্রে পর্যায়কাল কত হবে?</t>
+          <t>##PRESET:simple-pendulum[size:small]##
+একটি সরল দোলক একটি ট্রলির ছাদ থেকে ঝুলানো আছে। ট্রলিটি অনুভূমিকভাবে $a = 5.66\text{ ms}^{-2}$ ত্বরণে গতিশীল হলে দোলকটির কার্যকর দোলনকাল স্থির অবস্থার দোলনকালের কত গুণ হবে? ($g = 9.8\text{ ms}^{-2}$)।</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:spring-mass[size:medium]##</t>
+          <t>##PRESET:simple-pendulum[size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 42)।</t>
+          <t>কার্যকর ত্বরণ $g_{eff} = \\sqrt{g^2 + a^2} = \\sqrt{9.8^2 + 5.66^2} = \\sqrt{96.04 + 32.04} = \\sqrt{128.08} \\approx 11.317\\text{ ms}^{-2}$। অতএব $\\frac{T'}{T} = \\sqrt{\\frac{g}{g_{eff}}} = \\sqrt{\\frac{9.8}{11.317}} \\approx \\sqrt{0.8659} \\approx 0.9306 \\approx 0.931$।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>$T' = 0.932 T$</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5720,43 +5461,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য (সমস্যা 43)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য]
-##PRESET:pendulum(15)[size:medium]##
-যে স্থানে $g = 9.4\text{ m/s}^2$, সেখানে একটি সঠিক সেকেন্ড দোলকের কার্যকরী দৈর্ঘ্য কত মিটার হতে হবে?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+সরল ছন্দিত স্পন্দনে স্পন্দিত একটি কণার সমীকরণ $x = 0.08\sin(4\pi t)$ মিটার। কণাটি সাম্যাবস্থা থেকে কত সময় পর তার সর্বোচ্চ স্থিতিশক্তির অর্ধেক স্থিতিশক্তি অর্জন করবে?</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>##PRESET:pendulum(15)[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 43)।</t>
+          <t>স্থিতিশক্তি $U = \\frac{1}{2}m\\omega^2 x^2$ এবং সর্বোচ্চ স্থিতিশক্তি $U_{\\max} = \\frac{1}{2}m\\omega^2 A^2$। $U = \\frac{1}{2}U_{\\max} \\implies x^2 = \\frac{1}{2}A^2 \\implies x = \\frac{A}{\\sqrt{2}}$। সমীকরণে বসিয়ে: $\\frac{A}{\\sqrt{2}} = A\\sin(4\\pi t) \\implies \\sin(4\\pi t) = \\frac{1}{\\sqrt{2}} \\implies 4\\pi t = \\frac{\\pi}{4} \\implies t = \\frac{1}{16} \\times \\frac{1}{2} = \\frac{1}{32}\\text{ s} = 0.03125\\text{ s}$।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>সময় $t = 0.03125\\text{ s} = \\frac{1}{32}\\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5776,12 +5512,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>দোলক ঘড়ির পাহাড়ে সময় হারানো (সমস্যা 44)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5789,25 +5525,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: দোলক ঘড়ির পাহাড়ে সময় হারানো]
-একটি সেকেন্ড দোলক ঘড়িকে পাহাড়ের চূড়ায় নিয়ে গেলে এটি দিনে 6 সেকেন্ড সময় হারায়। পাহাড়টির উচ্চতা কত কিলোমিটার নির্ণয় কর। ($R = 6400\text{ km}$)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সরল ছন্দিত স্পন্দনের একটি পূর্ণ পর্যায়ের মধ্যে কত ভগ্নাংশ সময় জুড়ে কণার স্থিতিশক্তি তার গতিশক্তির চেয়ে বেশি থাকে?</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 44)।</t>
+          <t>$U &gt; K \\iff \\frac{1}{2}k x^2 &gt; \\frac{1}{2}k(A^2 - x^2) \\iff x^2 &gt; \\frac{A^2}{2} \\iff |x| &gt; \\frac{A}{\\sqrt{2}}$। প্রতি চতুর্থাংশে $x = A/\\sqrt{2}$ থেকে $x = A$ পর্যন্ত সময় $\\Delta t = \\frac{T}{4} - \\frac{T}{8} = \\frac{T}{8}$। পুরো চক্রে এমন ৪টি অংশ থাকায় মোট সময় $= 4 \\times \\frac{T}{8} = \\frac{T}{2}$ বা মোট পর্যায়কালের অর্ধেক সময়।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>মোট সময়ের অর্ধেক ($0.5 T$ বা $\\frac{1}{2}$ অংশ সময়)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5827,38 +5563,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দনে শক্তি বিভাজন (সমস্যা 45)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: সরল ছন্দিত স্পন্দনে শক্তি বিভাজন]
-একটি সরল ছন্দিত স্পন্দকের মোট যান্ত্রিক শক্তি $E = 8\text{ J}$ এবং বিস্তার $A = 3\text{ cm}$। সাম্যাবস্থা হতে কত দূরত্বে কণাটির গতিশক্তি বিভবশক্তির সমান হবে?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি টরশন দোলকে (Torsional Pendulum) $M = 2\text{ kg}$ ভরের এবং $R = 0.2\text{ m}$ ব্যাসার্ধের একটি চাকতি কেন্দ্রের মধ্য দিয়ে গমনকারী অক্ষের সাপেক্ষে একটি তারের সাহায্যে ঝুলানো আছে। তারের মোচড় ধ্রুবক $C = 1.6\text{ N}\cdot\text{m/rad}$ হলে চাকতিটির কৌণিক স্পন্দনের পর্যায়কাল কত?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 45)।</t>
+          <t>চাকতির জড়তার ভ্রামক $I = \\frac{1}{2}M R^2 = \\frac{1}{2}(2)(0.2)^2 = 0.04\\text{ kg}\\cdot\\text{m}^2$। টরশনাল দোলনকাল $T = 2\\pi\\sqrt{\\frac{I}{C}} = 2\\pi\\sqrt{\\frac{0.04}{1.6}} = 2\\pi\\sqrt{0.025} = 2\\pi(0.1581) \\approx 0.9935\\text{ s}$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>পর্যায়কাল $T = 0.993\\text{ s} \\approx 1.0\\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5878,12 +5614,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>দোলকের ত্বরণ ও সর্বোচ্চ বেগ (সমস্যা 46)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -5891,25 +5627,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: দোলকের ত্বরণ ও সর্বোচ্চ বেগ]
-একটি স্পন্দকের বিস্তার $A = 10\text{ cm}$ এবং পর্যায়কাল $T = 4\text{ s}$ হলে কণাটির সর্বোচ্চ দ্রুতি ($v_{max}$) এবং সর্বোচ্চ ত্বরণ ($a_{max}$) কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##PRESET:spring-mass-system[size:medium]##
+একটি স্প্রিং-ভর সিস্টেমে $m = 0.5\text{ kg}$ ভর এবং $k = 50\text{ N/m}$ স্প্রিং ধ্রুবক রয়েছে। ভরটিকে সাম্যাবস্থা হতে $10\text{ cm}$ টেনে ছেড়ে দেওয়া হলো। সাম্যাবস্থা অতিক্রম করার মুহূর্তে এর গতিশক্তি কত এবং সাম্যাবস্থা থেকে $6\text{ cm}$ দূরত্বে এর বেগ কত?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##PRESET:spring-mass-system[size:medium]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 46)।</t>
+          <t>সর্বোচ্চ গতিশক্তি $K_{\\max} = \\frac{1}{2}k A^2 = \\frac{1}{2}(50)(0.10)^2 = 0.25\\text{ J}$। কৌণিক কম্পাঙ্ক $\\omega = \\sqrt{\\frac{k}{m}} = \\sqrt{\\frac{50}{0.5}} = 10\\text{ rad/s}$। $x = 0.06\\text{ m}$-এ বেগ $v = \\omega\\sqrt{A^2 - x^2} = 10\\sqrt{0.10^2 - 0.06^2} = 10\\sqrt{0.0064} = 10(0.08) = 0.80\\text{ m/s}$।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>$K_{\\max} = 0.25\\text{ J}$, $v(6\\text{ cm}) = 0.80\\text{ m/s}$</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5929,38 +5665,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>তরল স্তম্ভের দোলনকাল (U-টিউব) (সমস্যা 47)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: তরল স্তম্ভের দোলনকাল (U-টিউব)]
-একটি U-নলে $h = 12\text{ cm}$ উচ্চতার পারদ স্তম্ভ রাখা আছে। একপাশে সামান্য চাপ দিয়ে ছেড়ে দিলে পারদ স্তম্ভের সরল ছন্দিত দোলনের পর্যায়কাল $T = 2\pi \sqrt{\frac{h}{g}}$ কত হবে?</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=3][size:small]##
+একটি গোলকাকার ফাঁপা গোলকের ভেতর একটি ক্ষুদ্র বস্তু ঘর্ষণহীনভাবে তলদেশ বরাবর সামান্য আন্দোলিত হয়। গোলকের অন্তর্ব্যাসার্ধ $R = 2.45\text{ m}$ হলে বস্তুটির স্পন্দনের পর্যায়কাল কত?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 47)।</t>
+          <t>ক্ষুদ্র কোণে গোলকের কেন্দ্র হতে তলদেশ পর্যন্ত দূরত্ব কার্যকর সরল দোলকের দৈর্ঘ্যের সমতুল্য ($L = R$)। পর্যায়কাল $T = 2\\pi\\sqrt{\\frac{R}{g}} = 2\\pi\\sqrt{\\frac{2.45}{9.8}} = 2\\pi\\sqrt{\\frac{1}{4}} = 2\\pi(0.5) = \\pi \\approx 3.1416\\text{ s}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>পর্যায়কাল $T = 3.14\\text{ s} = \\pi\\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5980,12 +5716,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>স্প্রিং-এর দোলন ও ভর পরিবর্তন (সমস্যা 48)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -5993,25 +5729,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: স্প্রিং-এর দোলন ও ভর পরিবর্তন]
-একটি স্প্রিং-এ $m_1 = 2\text{ kg}$ ভর ঝুলালে পর্যায়কাল হয় $T_1 = 1.0\text{ s}$। এর সাথে অতিরিক্ত $m_2 = 6\text{ kg}$ ভর যুক্ত করলে নতুন পর্যায়কাল কত হবে?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+দুটি সরল ছন্দিত স্পন্দনের সমীকরণ $x_1 = 3\sin(\omega t)$ এবং $x_2 = 4\cos(\omega t) = 4\sin(\omega t + \pi/2)$। এদের উপরিপাতনের ফলে সৃষ্ট লব্ধি তরঙ্গের বিস্তার এবং প্রারম্ভিক দশা কত হবে?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 48)।</t>
+          <t>দশা পার্থক্য $\\Delta\\phi = \\frac{\\pi}{2}$। লব্ধি বিস্তার $A = \\sqrt{A_1^2 + A_2^2 + 2A_1 A_2 \\cos(\\pi/2)} = \\sqrt{3^2 + 4^2} = 5.0\\text{ m}$। দশা কোণ $\\tan\\delta = \\frac{A_2}{A_1} = \\frac{4}{3} \\implies \\delta = \\arctan(4/3) \\approx 53.13^\\circ$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>লব্ধি বিস্তার $A = 5.0\\text{ m}$, প্রারম্ভিক দশা $\\delta = 53.13^\\circ = 0.927\\text{ rad}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6031,38 +5767,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>দোলকের দোলন বিস্তার হ্রাস ও শক্তি (সমস্যা 49)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: দোলকের দোলন বিস্তার হ্রাস ও শক্তি]
-একটি অবমন্দিত সরল দোলকের বিস্তার প্রতি ১০টি দোলনে প্রাথমিক বিস্তারের $4\%$ হ্রাস পায়। এই সময়ে দোলকটির মোট শক্তি শতকরা কত হ্রাস পাবে?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কণা সরল ছন্দিত স্পন্দনে রয়েছে যার মোট যান্ত্রিক শক্তি $E = 100\text{ J}$। যখন কণাটির সরণ বিস্তারের এক-চতুর্থাংশ ($x = A/4$), তখন তার গতিশক্তি এবং স্থিতিশক্তির অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 49)।</t>
+          <t>স্থিতিশক্তি $U = \\frac{1}{2}k x^2 = \\frac{1}{2}k (A/4)^2 = \\frac{E}{16} = \\frac{100}{16} = 6.25\\text{ J}$। গতিশক্তি $K = E - U = 100 - 6.25 = 93.75\\text{ J} = \\frac{15}{16}E$। অনুপাত $\\frac{K}{U} = \\frac{15/16}{1/16} = 15 : 1$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$K : U = 15 : 1$, $K = 93.75\\text{ J}, U = 6.25\\text{ J}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6082,12 +5818,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>কৌণিক সরল ছন্দিত গতি ও টর্ক (সমস্যা 50)</t>
+          <t>উন্নত স্পন্দন, দোলক ও শক্তি বিশ্লেষণ (Advanced Oscillations &amp; Energy Analysis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6095,25 +5831,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: কৌণিক সরল ছন্দিত গতি ও টর্ক]
-একটি সুষম দণ্ডের একপ্রান্তে অনুভূমিক পেরেকের ওপর ঝুলিয়ে সামান্য দুলিয়ে দিলে এর দোলনকাল কত হবে? ($L = 6\text{ m}, g = 9.8\text{ m/s}^2$)</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=1,h=5][size:small]##
+একটি জটিল দোলকের (Compound pendulum) ভরকেন্দ্রগামী অক্ষের সাপেক্ষে চক্রগতির ব্যাসার্ধ $k_c$ এবং ঝুলন বিন্দু হতে ভরকেন্দ্রের দূরত্ব $l$। পর্যায়কাল ন্যূনতম হওয়ার শর্ত প্রমাণ কর এবং ন্যূনতম পর্যায়কালের রাশিমালা নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=1,h=5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>সরল ছন্দিত স্পন্দন ও সরল দোলকের গতীয় সমীকরণ ব্যবহার করে নির্ণয় (সমস্যা 50)।</t>
+          <t>দোলনকাল $T = 2\\pi\\sqrt{\\frac{k_c^2 + l^2}{gl}}$। $T$-কে ন্যূনতম করতে $\\frac{d}{dl}\\left(\\frac{k_c^2 + l^2}{l}\\right) = 0 \\implies 1 - \\frac{k_c^2}{l^2} = 0 \\implies l = k_c$। এই শর্তে সমতুল্য দৈর্ঘ্য $L = \\frac{k_c^2 + k_c^2}{k_c} = 2k_c$, ফলে $T_{\\min} = 2\\pi\\sqrt{\\frac{2k_c}{g}}$।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>পর্যাবৃত্ত গতির সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>শর্ত $l = k_c$, ন্যূনতম পর্যায়কাল $T_{\\min} = 2\\pi\\sqrt{\\frac{2k_c}{g}}$</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
